--- a/docs/knowledge-base/exports/Beauty_Lounge_Behandlungskatalog.xlsx
+++ b/docs/knowledge-base/exports/Beauty_Lounge_Behandlungskatalog.xlsx
@@ -9,9 +9,10 @@
   <sheets>
     <sheet name="Alle Leistungen" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Beauty-Needs-Zuordnung" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Nur intern (Kalenderblöcke)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alle Leistungen'!$A$1:$E$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Alle Leistungen'!$A$1:$I$159</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -53,7 +54,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -63,6 +64,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="009A4B66"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007A7A7C"/>
       </patternFill>
     </fill>
   </fills>
@@ -80,18 +86,16 @@
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -457,14 +461,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E119"/>
+  <dimension ref="A1:I159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -490,1629 +498,2873 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Nachbereitung (Min)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Online buchbar</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Abkürzung</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Beschreibung</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Studiolution-ID</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>✨ Neukunden Behandlungen</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>SkinCare &amp; Hairfree Event am 5.9.</t>
+          <t>Start Up Behandlung</t>
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>GEPLANTES SkinCare &amp; Hairfree Event am Sa. 5.9.2026 von 9:00-14:00 Uhr. Gratis Hairfree Termine und Formularanmeldung.</t>
+        <v>90</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>StartUp Beh.</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Kennenlern Behandlung für Neukunden. Nach einer digitalen Hautanalyse, besprechen und erstellen wir einen individuellen Pflege- &amp; Behandlungsplan, um Ihr Wunsch Hautergebnis schnellstmöglich zu erreichen. Im Anschluss darf eine intensive Behandlung passend zum Hautzustand, nicht fehlen.</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>424011</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>NEU FORMA - Hautstraffung (Radiofrequenz)</t>
+          <t>Klassische Gesichts Behandlungen</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>FORMA GRATIS Beratungsgespräch</t>
+          <t>Clean &amp; Activ Behandlung</t>
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>Gratis Beratungsgespräch inklusive einer ausführlichen Aufklärung über die FORMA Radiofrequenz.</t>
+        <v>50</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Clean Beh.</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Eine intensive Ausreinigungsbehandlung, für ein sauberes und geklärtes Hautbild. Welcome Rituale, Pinselmassage, individuelles Peeling, intensive Ausreinigung, Reinigungsmaske, Abschlusspflege. NUR bei tiefliegenden Unreinheiten zu empfehlen.</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>424012</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>NEU FORMA - Hautstraffung (Radiofrequenz)</t>
+          <t>Klassische Gesichts Behandlungen</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>FORMA Beratungsgespräch + Digitaler Hautanalyse KI</t>
+          <t>Relax Behandlung</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>Umfangreiches Beratungsgespräch inklusive ausführlicher Aufklärung über FORMA Radiofrequenz und digitaler KI-Hautanalyse.</t>
+        <v>70</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Relax Beh.</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Entspannende Verwöhn Behandlung für eine kleine Auszeit vom Alltag. Wir verwöhnen Ihre Haut ganz individuell. Nach unseren Welcome Ritualen, Reinigung mit einer Pinselmassage, Peeling, ausreinigung, Wirkstoff Ampulle, verwöhnenden Massage, Maske und Abschlusspflege. Gesicht +Hals + Dekolleté</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>424014</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>NEU FORMA - Hautstraffung (Radiofrequenz)</t>
+          <t>Aqua Dermabrasion</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>ANGEBOT 5+1 Kur</t>
+          <t>AquaDerm</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>FORMA Kennenlern Aktion: 5x FORMA Behandlungen bezahlen + 1 gratis. Bitte zu einer Kur dazu buchen.</t>
+        <v>60</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>AquaDerm</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Glow to Go. Ein sofort Effekt, nach nur einer Behandlung. Mittels Vakuum wird die Haut Tiefengereinigt, es entsteht ein sauberes und reines Hautgefühl. Die abgestimmten Wirkstoffe versorgen die Haut intensiv. Für ein gepflegtes, aufgepolstertes Ergebnis. Gesicht +Hals +Dekolleté</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>424019</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>NEU FORMA - Hautstraffung (Radiofrequenz)</t>
+          <t>Fruchtsäure Behandlungen</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>ANGEBOT 7+2 Kur</t>
+          <t>ASA PEEL Fruchtsäure</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>FORMA Kennenlern Aktion: 7x FORMA Behandlungen bezahlen + 2 gratis. Bitte zu einer Kur dazu buchen.</t>
+        <v>50</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>ASA PEEL</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Schicht für Schicht eine neue Haut.ASA ist eine abtragende Fruchtsäure Kombination, um die Hautoberfläche zu verbessern und zu verfeinern. Für ein ebenmäßigeres Hautbild, um Linien -Fältchen- Pigmente zu minimieren. Wir beraten Sie gerne. NUR buchbar von Sep./Okt. - März (wg. der UV-Strahlung)</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>424020</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>NEU FORMA - Hautstraffung (Radiofrequenz)</t>
+          <t>Fruchtsäure Behandlungen</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>FORMA Augen</t>
+          <t>ASA Fruchtsäure KUR</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>129</v>
+        <v>447</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>FORMA strafft gezielt den kompletten Augenbereich. Elastizitätsverlust am oberen Augenlid wird minimiert.</t>
+        <v>50</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>ASA Peel KUR</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Um ein optimales Ergebnis zu erzielen, EMPFEHLEN wir unseren Kunden, eine 3-er ASA KUR zu machen. Bei einer KUR, bekommst du GRATIS HEIMPFLEGE im Wert von 30€ dazu. Wir beraten dich gerne persönlich.</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>424021</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>NEU FORMA - Hautstraffung (Radiofrequenz)</t>
+          <t>✨VIP Treatments by Klapp SkinCare</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>FORMA Jawline inkl. unteren Wangenbereich</t>
+          <t>Luxus Treatments</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Doppelkinn inkl. unterem Wangenbereich. FORMA strafft gezielt die Gesichtskonturen, Elastizitätsverlust wird minimiert.</t>
+        <v>80</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Luxus Treat</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Erleben Sie eine unserer intensiven Anti -Age Erlebnis Behandlungen von Klapp SkinCare. Wir überlegen vor Ort zusammen, welches der Treatments am besten zu Ihnen &amp; Ihrer Haut passt, um ein optimales Ergebnis zu erreichen -&gt; *Vitamin Power Boost *Hyaluron Infusion *Caviar *Hyaluronic o.ä.</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>424023</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>NEU FORMA - Hautstraffung (Radiofrequenz)</t>
+          <t>Wimpern &amp; Augenbrauen           • Einzelbehandlung</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>FORMA Hals</t>
+          <t>Wimpern färben</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>129</v>
+        <v>28</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>FORMA strafft gezielt die Gesichtskonturen, Elastizitätsverlust wird stark minimiert.</t>
+        <v>15</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Wimpern fä</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Wimpern färben AUSSERHALB einer Behandlung</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>424026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>NEU FORMA - Hautstraffung (Radiofrequenz)</t>
+          <t>Wimpern &amp; Augenbrauen           • Einzelbehandlung</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>FORMA 1 Zone</t>
+          <t>Augenbrauen färben</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>119</v>
+        <v>18</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>FORMA strafft gezielt die Gesichtskonturen, Elastizitätsverlust wird stark minimiert.</t>
+        <v>10</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Brauen fä</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Augenbrauen färben AUSSERHALB einer Behandlung</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>424027</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>NEU FORMA - Hautstraffung (Radiofrequenz)</t>
+          <t>Wimpern &amp; Augenbrauen           • Einzelbehandlung</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>FORMA 2 Zonen</t>
+          <t>Augenbrauen zupfen</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>219</v>
+        <v>18</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>FORMA strafft gezielt die Gesichtskonturen, Elastizitätsverlust wird stark minimiert.</t>
+        <v>10</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Brauen zpf</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Augenbrauen zupfen AUSSERHALB einer Behandlung</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>424028</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>NEU FORMA - Hautstraffung (Radiofrequenz)</t>
+          <t>Wimpern &amp; Augenbrauen           • Einzelbehandlung</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>FORMA 3 Zonen</t>
+          <t>Augenbrauen Wachsen</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>319</v>
+        <v>18</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>105</v>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>FORMA strafft gezielt die Gesichtskonturen, Elastizitätsverlust wird stark minimiert.</t>
+        <v>10</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Brauen Wx</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Augenbrauen wachsen AUSSERHALB einer Behandlung</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>424029</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>NEU FORMA - Hautstraffung (Radiofrequenz)</t>
+          <t>Wimpernlifting - Browlift</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>FORMA 6er KUR</t>
+          <t>Wimpernlifting inkl. Keratin Versiegelung</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>10% Rabatt auf die ausgewählte FORMA Kur. Bitte zur FORMA-Behandlung dazu buchen.</t>
+        <v>50</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Wimpern Lift</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>Verleiht Ihren Naturwimpern einen natürlichen und perfekten Augenaufschlag. Die Wimpern wirken wie natürlich verlängert. Das Ergebnis hält je nach Wimper, ca.4-8 Wochen. Wimpern färben bitte extra dazu buchen!</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>424031</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>NEU FORMA - Hautstraffung (Radiofrequenz)</t>
+          <t>Wimpernlifting - Browlift</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>FORMA 8er KUR</t>
+          <t>Wimpernwelle inkl. Keratin Versiegelung</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>10% Rabatt auf die ausgewählte FORMA Kur. Bitte zur FORMA-Behandlung dazu buchen.</t>
+        <v>50</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Wimpern Well</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>Die Wimpernwelle bringt neuen Schwung in Ihre Naturwimpern. Gerade Wimpern dürfen endlich auch mit einem natürlichen Schwung strahlen. Das Ergebnis hält je nach Wimper, ca. 4-8 Wochen. Wimpern färben bitte dazu buchen!</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>424032</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>NEU DIOLAZE - Dauerhafte Haarentfernung</t>
+          <t>Wimpernlifting - Browlift</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>GRATIS Beratungsgespräch Inkl. Haar- &amp; Hautanalyse</t>
+          <t>Browlift inkl. Keratin Verssiegelung</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Informationsgespräch zur dauerhaften Haarentfernung.</t>
+        <v>35</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Brow Lift</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Lässt Ihre Augenbrauen voller und dichter erscheinen. Ein tolles Ergebnis für jeden der das Gefühl hat, die Brauen dürften natürlich voller aussehen. Brauen färben und zupfen bitte extra buchen !</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>424033</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>NEU DIOLAZE - Dauerhafte Haarentfernung</t>
+          <t>Wellness Maniküre</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>FIRST DATE! Laser</t>
+          <t>Wellness Maniküre</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>Zur ersten Laserbehandlung dazu buchen.</t>
+        <v>30</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Welln.Mani</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>Intensive Hand- und Nagelpflege mit hochwertigen Produkten von Alessandro. Ein wohltuendes Handbad, ein sanft abtragendes Peeling, eine intensive Nagel- &amp;Hand Behandlung und zum Abschluss eine entspannende Handmassage. Pure Pflege und Entspannung für deine Hände.</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>424034</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>NEU DIOLAZE - Dauerhafte Haarentfernung</t>
+          <t>Wellness Maniküre</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Oberlippe</t>
+          <t>+ Nagellack Maniküre</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>Dauerhafte Haarentfernung Oberlippe.</t>
+        <v>10</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>+Lack Manik</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>Wir verschönern ihre Fingernägel mit einem hochwertigem Alessandro Nagellack. 4 Schichten -&gt; Unterlack, 2x Nagellack, Überlack. Der Nagellack kann NUR in Verbindung mit einer Wellness Maniküre gebucht werden !!!</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>424035</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>NEU DIOLAZE - Dauerhafte Haarentfernung</t>
+          <t>Wellness Maniküre</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Kinn</t>
+          <t>+ UV- Nagellack Maniküre</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>Dauerhafte Haarentfernung Kinn.</t>
+        <v>15</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>+ProLaq</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>Hochwertiger UV-Nagellack von Alessandro, der deine Nägel ca.14Tage strahlen lässt! Für perfekt gepflegte Nägel. Der ProLaq ist NUR in Verbindung mit einer Wellness Maniküre buchbar !!!</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>424036</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>NEU DIOLAZE - Dauerhafte Haarentfernung</t>
+          <t>Gel Verstärkung Fingernägel</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Brust</t>
+          <t>Natur Nagel Verstärkung NEU</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>Dauerhafte Haarentfernung Brust.</t>
+        <v>60</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>NatNagVerst</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>Eine Verstärkung der Natur Nagel mit Gel, ohne Verlängerung. Farbe oder French müssen dazu gebucht werden!</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>424038</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>NEU DIOLAZE - Dauerhafte Haarentfernung</t>
+          <t>Gel Verstärkung Fingernägel</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Bauch</t>
+          <t>Neue Gel Modellage mit Verlängerung Tips/Schablone</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>Dauerhafte Haarentfernung Bauch.</t>
+        <v>80</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Komplett Set</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>Neue Gel Modellage mit einer Verlängerung, mit Tip‘s oder der Schablonen Technik. Farbe oder French müssen dazu gebucht werden!</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>424040</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>NEU DIOLAZE - Dauerhafte Haarentfernung</t>
+          <t>Gel Verstärkung Fingernägel</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Rücken</t>
+          <t>Auffüllen Gel Nägel</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>149</v>
+        <v>89</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>Dauerhafte Haarentfernung Rücken.</t>
+        <v>60</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Auffüllen</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Auffüllen der Gel Nägel nach ca. 3-4 Wochen</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>424041</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>NEU DIOLAZE - Dauerhafte Haarentfernung</t>
+          <t>Gel Verstärkung Fingernägel</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Achseln</t>
+          <t>+ Farbgel / French/ Babyboomer</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>Dauerhafte Haarentfernung Achseln.</t>
+        <v>10</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Farbgel</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>Farbgel / French/ Babyboomer als extra zu einer Gel Nagel Behandlung</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>424043</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>NEU DIOLAZE - Dauerhafte Haarentfernung</t>
+          <t>Gel Verstärkung Fingernägel</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Oberarm</t>
+          <t>Einzelner Nagel Neu Auffüllen</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>119</v>
+        <v>8.5</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Dauerhafte Haarentfernung Oberarm.</t>
+        <v>5</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Nagel Neu Au</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Einzelner Nagel Neu beim Auffüllen mit Tip/ Schablone</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>424044</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>NEU DIOLAZE - Dauerhafte Haarentfernung</t>
+          <t>Gel Verstärkung Fingernägel</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Unterarme</t>
+          <t>Einzelner Nagel Neu Zwischendurch</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>109</v>
+        <v>13</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>Dauerhafte Haarentfernung Unterarme.</t>
+        <v>10</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Nagel Neu Zw</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>Einzelner Nagel Neu Zwischendurch</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>424045</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>NEU DIOLAZE - Dauerhafte Haarentfernung</t>
+          <t>Gel Verstärkung Fingernägel</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Bikini Zone</t>
+          <t>Nachfeilen inkl. Versiegelung 30min</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Dauerhafte Haarentfernung Bikini Zone.</t>
+        <v>30</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Nachf.Vers30</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Nachfeilen inkl. Versiegelung 30min</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>424046</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>NEU DIOLAZE - Dauerhafte Haarentfernung</t>
+          <t>Gel Verstärkung Fingernägel</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Intim Bereich</t>
+          <t>Nachfeilen inkl. Versiegelung 40min</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>139</v>
+        <v>63</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>Dauerhafte Haarentfernung Intimbereich.</t>
+        <v>45</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Nachf.Vers40</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>Nachfeilen inkl. Versiegelung 40min</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>424047</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>NEU DIOLAZE - Dauerhafte Haarentfernung</t>
+          <t>Gel Verstärkung Fingernägel</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Bein Oberschenkel</t>
+          <t>Gel entfernen inkl. Pflege 30min</t>
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>159</v>
+        <v>52</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>Dauerhafte Haarentfernung Oberschenkel.</t>
+        <v>30</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Gel entf.30</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Gel entfernen inkl. Pflege 30min</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>424048</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>NEU DIOLAZE - Dauerhafte Haarentfernung</t>
+          <t>Gel Verstärkung Fingernägel</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Bein Unterschenkel</t>
+          <t>Gel entfernen inkl. Pflege 40min</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>149</v>
+        <v>65</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>Dauerhafte Haarentfernung Unterschenkel.</t>
+        <v>40</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Gel entf.40</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>Gel Modellage entfernen inklusive Pflege. Bitte haben Sie Verständnis dafür das wir KEINE FREMDARBEITEN mehr entfernen!</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>424049</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>NEU DIOLAZE - Dauerhafte Haarentfernung</t>
+          <t>➕ Zusatzbehandlungen</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Herren Brust</t>
+          <t>Oberlippe wachsen</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>115</v>
+        <v>20</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>Dauerhafte Haarentfernung Herren Brust.</t>
+        <v>10</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Oberl.Wx</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Oberlippe wachsen</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>424050</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>NEU DIOLAZE - Dauerhafte Haarentfernung</t>
+          <t>➕ Zusatzbehandlungen</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Herren Bauch</t>
+          <t>Oberlippe + Kinn wachsen</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>129</v>
+        <v>30</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>Dauerhafte Haarentfernung Herren Bauch.</t>
+        <v>15</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Oberl.+Ki.Wx</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>Oberlippe + Kinn wachsen</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>424051</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>NEU DIOLAZE - Dauerhafte Haarentfernung</t>
+          <t>➕ Zusatzbehandlungen</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Herren Nacken</t>
+          <t>Rücken Wachsen 20min normal</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>Dauerhafte Haarentfernung Herren Nacken.</t>
+      <c r="E31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Rücken Wx.20</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Rücken Wachsen 20min Normal viel</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>424057</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>NEU DIOLAZE - Dauerhafte Haarentfernung</t>
+          <t>Wimpernlifting - Browlift</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Herren Schultern</t>
+          <t>+ Wimpern färben Lifting/ Welle</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>89</v>
+        <v>19</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>Dauerhafte Haarentfernung Herren Schultern.</t>
+        <v>10</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>+WL-Wimp fär</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>Wimpern färben als extra, zu einem Wimpernlifting/ Welle</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>424059</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>NEU DIOLAZE - Dauerhafte Haarentfernung</t>
+          <t>Wimpernlifting - Browlift</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Herren Rücken</t>
+          <t>+ Augenbrauen färben Browlift</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>169</v>
+        <v>15</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>Dauerhafte Haarentfernung Herren Rücken.</t>
+        <v>5</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>+BL-Br färb</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Augenbrauen färben als extra, zu einem Browlift</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>424060</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>NEU DIOLAZE - Dauerhafte Haarentfernung</t>
+          <t>Wellness Fußpflege</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Herren Teil-Rücken</t>
+          <t>Wellness Fußpflege</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>Dauerhafte Haarentfernung Herren Teil-Rücken.</t>
+        <v>40</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Welln.Fußpfl</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>Unsere Füße tragen uns durch unser ganzes Leben. Wir schenken ihren Füßen eine Auszeit vom Alltag, mit einem wohltuendes warmen Fußbad, einer intensiven Fußbehandlung von Nägeln, Nagelhaut und Hornhaut. Zum Abschluss eine entspannende Fußmassage mit hochwertigen GEHWOL Produkten.</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>424063</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>NEU DIOLAZE - Dauerhafte Haarentfernung</t>
+          <t>Wellness Fußpflege</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Herren Achseln</t>
+          <t>+ Nagellack Fuß</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>Dauerhafte Haarentfernung Herren Achseln.</t>
+        <v>10</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>+Lack Fuß</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Wir verschönern Ihre Fußnägel mit einem hochwertigem Alessandro Nagellack. 4- Schichten für ca.4 Wo. Haltbarkeit -&gt; Unterlack, 2x Farblack, Überlack. Der Nagellack kann NUR in Verbindung mit einer Wellness Fußpflege gebucht werden !!!</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>424064</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>NEU DIOLAZE Pakete</t>
+          <t>Wellness Fußpflege</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>MUST HAVE Achseln + Bikini</t>
+          <t>+ UV -Nagellack Fuß</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>155</v>
+        <v>31</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>Kombi-Paket dauerhafte Haarentfernung.</t>
+        <v>20</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>+UVLack Fuß</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>Wir verschönern ihre Fußnägel mit einem hochwertigem Alessandro UV -Nagellack. Wir arbeiten in 4 -Schichten für ca. 4-6 Wo. Haltbarkeit -&gt; Base Coat, 2x UV -Farblack/French, Top Coat. Der UV -Nagellack kann NUR in Verbindung mit einer Wellness Fußpflege gebucht werden !!!</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>424065</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>NEU DIOLAZE Pakete</t>
+          <t>➕ Zusatzbehandlungen</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>MUST HAVE Achseln + Intim Bereich</t>
+          <t>+ Wimpern färben</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>199</v>
+        <v>19</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>Kombi-Paket dauerhafte Haarentfernung.</t>
+        <v>10</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>+Wimp. färb.</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>NUR in Verbindung mit einer anderen Behandlung buchbar !!!</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>431836</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>NEU DIOLAZE Pakete</t>
+          <t>➕ Zusatzbehandlungen</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>MUST HAVE Achseln + Intim + Unterschenkel</t>
+          <t>+ Augenbrauen färben</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>315</v>
+        <v>14</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>Kombi-Paket dauerhafte Haarentfernung.</t>
+        <v>5</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>+Br.färben</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>NUR in Verbindung mit einer anderen Behandlung buchbar !!!</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>431837</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>NEU DIOLAZE Pakete</t>
+          <t>➕ Zusatzbehandlungen</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>MUST HAVE Achseln + Intim Bereich + Beine Komplett</t>
+          <t>+ Augenbrauen zupfen</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>439</v>
+        <v>15</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="E39" s="5" t="inlineStr">
-        <is>
-          <t>Kombi-Paket dauerhafte Haarentfernung.</t>
+        <v>5</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>+Br.zpf.</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>NUR in Verbindung mit einer anderen Behandlung buchbar !!!</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>431838</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>NEU DIOLAZE Pakete</t>
+          <t>➕ Zusatzbehandlungen</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Oberlippe + Kinn</t>
+          <t>+ Augenbrauen Wachsen</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>79</v>
+        <v>15</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>Kombi-Paket dauerhafte Haarentfernung.</t>
+        <v>5</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>+Br.Wx.</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>NUR in Verbindung mit einer anderen Behandlung buchbar!</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>431839</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>NEU DIOLAZE Pakete</t>
+          <t>Wimpern &amp; Augenbrauen           • Einzelbehandlung</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Kinn + Hals</t>
+          <t>Augenbrauen schneiden</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>89</v>
+        <v>3.5</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>Kombi-Paket dauerhafte Haarentfernung.</t>
+        <v>0</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>Br.schneiden</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>Augenbrauen schneiden, AUSSERHALB einer Behandlung</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>431881</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>NEU DIOLAZE Pakete</t>
+          <t>➕ Zusatzbehandlungen</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Arme Komplett</t>
+          <t>+ Augenbrauen schneiden</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>Kombi-Paket dauerhafte Haarentfernung.</t>
+        <v>0</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>+Br.schneid.</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr"/>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>431882</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>NEU DIOLAZE Pakete</t>
+          <t>➕ Zusatzbehandlungen</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Beine Komplett</t>
+          <t>+ Ampulle</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>275</v>
+        <v>12</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>Kombi-Paket dauerhafte Haarentfernung.</t>
+        <v>5</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>+Ampulle</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>NUR in Kombination mit einer Kosmetik Behandlung buchbar!!!</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>431883</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>NEU DIOLAZE Pakete</t>
+          <t>➕ Zusatzbehandlungen</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Herren Brust + Bauch</t>
+          <t>+ Spezial Maske</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>199</v>
+        <v>15</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>Kombi-Paket dauerhafte Haarentfernung.</t>
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>+Maske</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>NUR als EXTRA zu einer Kosmetik Behandlung buchbar.</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>431884</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>NEU DIOLAZE Pakete</t>
+          <t>➕ Zusatzbehandlungen</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Herren Brust + Bauch + Rücken</t>
+          <t>+ Kinn/ Oberlippe zupfen</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>329</v>
+        <v>14</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>Kombi-Paket dauerhafte Haarentfernung.</t>
+        <v>5</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>+Ober/Ki.zpf</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>Oberlippe und/oder Kinn zupfen. NUR in Verbindung mit einer anderen Behandlung buchbar !!!</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>432022</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>NEU DIOLAZE Pakete</t>
+          <t>Wellness Fußpflege</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Herren Nacken + Schulter</t>
+          <t>+ Fuß Nagel Gel Aufbau pro Nagel</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>Kombi-Paket dauerhafte Haarentfernung.</t>
+        <v>5</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>+FußGel Aufb</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>Nagelaufbau mit Gel/ Reperatur</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>432808</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>NEU DIOLAZE Pakete</t>
+          <t>Wellness Fußpflege</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Herren Rücken + Schulter</t>
+          <t>Fuß Extra Behandlung</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>229</v>
+        <v>20</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>Kombi-Paket dauerhafte Haarentfernung.</t>
+        <v>10</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>Fuß Extra</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>Zwischendurch Termin, Notfall Rep. oder sonstiges</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>432809</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>NEU DIOLAZE Pakete</t>
+          <t>Wellness Maniküre</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Herren Rücken + Schulter + Nacken</t>
+          <t>Uv Lack runter machen</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>259</v>
+        <v>25</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>Kombi-Paket dauerhafte Haarentfernung.</t>
+        <v>15</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Uv Lack ab</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>Wenn ein Kunde einen alten Uv Lack von wo anders runter gemacht haben möchte</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>435593</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>NEU DIOLAZE Pakete</t>
+          <t>Gel Verstärkung Fingernägel</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Herren Arme Komplett</t>
+          <t>Farbgel Neu inkl.Versiegelung</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>219</v>
+        <v>30</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>Kombi-Paket dauerhafte Haarentfernung.</t>
+        <v>20</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>Farbgel neu</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr"/>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>443338</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>NEU DIOLAZE Pakete</t>
+          <t>Wellness Maniküre</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Herren Beine Komplett</t>
+          <t>Uv Lack Reparatur</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>295</v>
+        <v>8</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>Kombi-Paket dauerhafte Haarentfernung.</t>
+        <v>5</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>Uv Lack Rep.</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr"/>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>443430</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Neukunden Behandlungen</t>
+          <t>Micro Needling</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Start Up Behandlung</t>
+          <t>Micro Needling</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
         <v>149</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>Kennenlernbehandlung für Neukunden. Nach digitaler Hautanalyse wird ein individueller Pflege- &amp; Behandlungsplan erstellt, anschließend eine passende intensive Behandlung.</t>
+        <v>60</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>MicroNeedl</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>Micro Needling ist eine Intensive Behandlung um den natürlichen Selbstheilungsprozess  der Haut anzuregen. Die Hautstruktur wird deutlich verbessert. Pickelmale, Narben, Unebenheiten und Faltentiefe werden bei einer KUR Behandlung effektiv vermindert. Beachte die AUSFALLZEIT !</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>450801</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Digitale Hautanalyse mit KI</t>
+          <t>Wimpernlifting - Browlift</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Hautsprechstunde Hautanalyse</t>
+          <t>Modell Wimpern</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>Ausführliche Hautanalyse-Beratung.</t>
+        <v>5</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>Modell Wimp</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr"/>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>450804</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Digitale Hautanalyse mit KI</t>
+          <t>Wellness Fußpflege</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>+ Digitale Hautanalyse</t>
+          <t>+ SPA Fuß</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>KI-gestützte digitale Hautanalyse als Zusatz.</t>
+      <c r="E53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>+Spa Fuß</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>Noch mehr Wellness für ihre Füße. Ein abtragendes und aktivierendes Peeling, um die abgestorbenen Hautschüppchen abzutragen. Es folgt ein pflegendes Serum, eine intensive Fußpackung und das beste kommt zum Schluss, eine wohltuende Fußmassage. Peeling, Serum, Fußpackung, Fußassage.</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>458805</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Digitale Hautanalyse mit KI</t>
+          <t>Wellness Maniküre</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Gratis Hautanalyse Gutschein</t>
+          <t>+ SPA Hand</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>Nur mit Gutschein buchbar.</t>
+        <v>20</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>+Spa Hand</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>Noch mehr Wellness für ihre Hände. Ein abtragendes und aktivierendes Peeling, um die abgestorbenen Hautschüppchen runter zu nehmen. Dann folgt ein pflegendes Serum, eine intensive Handpackung und das beste kommt zum Schluss, eine wohltuende Handmassage. Peeling, Serum, Handpackung, Handmassage.</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>458806</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Aktuelle Angebote</t>
+          <t>Micro Needling</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Vitamin C Fresh Up Power</t>
+          <t>+ Hals</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>159</v>
+        <v>20</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>Kombination aus Mikrodermabrasion und Vitamin C für ein frisches, ebenmäßiges Hautbild und Glow.</t>
+        <v>5</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>+ Hals</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>+Hals. NUR in Kombination mit der Soft/ Micro Needling Behandlung buchbar !!!</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>464630</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Aktuelle Angebote</t>
+          <t>Micro Needling</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>AquaDerm meets Soft Needling Exosome</t>
+          <t>+ Dekolleté</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>225</v>
+        <v>25</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>Intensive Kombination: mehr Glow, Balance, Regeneration. Tiefenreinigung, Hyaluronsäure, Exosome, Hautbarriere stärken, porenverfeinernd, aufpolsternd.</t>
+        <v>10</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>+ Dekollete</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>+Dekollete. NUR in Kombination mit der Soft/ Micro Needling Behandlung buchbar !!!</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>464633</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Aktuelle Angebote</t>
+          <t>✨TOP Kombi Behandlungen</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Soft Needling Exosome</t>
+          <t>Beautiful Hand &amp; Fuß</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>139</v>
+        <v>169</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>Für müde, gestresste Haut im Ungleichgewicht. Zellregeneration, Hautbarriere stärken, Mikrozirkulation fördern.</t>
+        <v>110</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>Beauty Ha&amp;Fu</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr"/>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>464640</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Aktuelle Angebote</t>
+          <t>Wellness Fußpflege</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>OnTop Hals Dekolleté (Soft Needling/Needling/Micro)</t>
+          <t>+ Fußmassage</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t>Zusatz Hals/Dekolleté zu jeder Needling-/Micro-Behandlung.</t>
+        <v>5</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>+Fußmassage</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>Als Wellness Zusatz können Sie sich eine wohltuende Fußmassage, für eine Aktivierung des Nervensystems und als Auszeit, zu der Wellness Fußpflege dazu buchen.</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>464642</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>TOP Kombi Behandlungen</t>
+          <t>✨ Events ✨</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>MicroDerm meets AquaDerm</t>
+          <t>Chrismas Shopping Event</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t>Intensives Erlebnis mit sofortigem Glow, verfeinertem Hautbild, minimierten Linien.</t>
+        <v>5</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>Xmas Shoppin</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr"/>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>470445</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>TOP Kombi Behandlungen</t>
+          <t>Klassische Gesichts Behandlungen</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Soft Needling meets Hyaluron</t>
+          <t>Extra Zeit Clean Beh.</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>239</v>
+        <v>9.5</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="E60" s="5" t="inlineStr">
-        <is>
-          <t>Soft Needling + 3-fach Hyaluronsäure. Sofort-Ergebnis: Glow + Aufgepolstert.</t>
+        <v>5</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>+Extra Zeit</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr"/>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>471166</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>VIP Treatments by Klapp SkinCare</t>
+          <t>Wellness Maniküre</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Luxus Treatments</t>
+          <t>Polieren</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>179</v>
+        <v>8</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="E61" s="5" t="inlineStr">
-        <is>
-          <t>Intensive Anti-Age-Erlebnisbehandlung, individuell aus Vitamin Power Boost / Hyaluron Infusion / Caviar / Hyaluronic zusammengestellt.</t>
+        <v>5</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>Politur</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr"/>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>495038</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>VIP Treatments by Klapp SkinCare</t>
+          <t>✨VIP Treatments by Klapp SkinCare</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Deluxe Treatments</t>
+          <t>Repagen Exclusive Treatment</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>205</v>
+        <v>229</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="E62" s="5" t="inlineStr">
-        <is>
-          <t>Deluxe Regenerationsbehandlung, individuell aus CellPro / Diamond / ExoGen zusammengestellt.</t>
+        <v>100</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>Repagen Excl</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>Hauterneuerung {ASA Fruchtsäure} kombiniert mit einem aktiven Lifting Komplex (Repagen Exclusive).Die Kombi trägt dazu bei, dass das Hautbild in neuem Glanz erstrahlt. Zudem wirkt die Haut glatter, praller und intensiv regeneriert. Müde Haut bekommt einen tollen Glow.</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>504981</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>VIP Treatments by Klapp SkinCare</t>
+          <t>Wellness Fußpflege</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Repagen Exclusive Treatment</t>
+          <t>+ Temponade</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>229</v>
+        <v>1.5</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="E63" s="5" t="inlineStr">
-        <is>
-          <t>Hauterneuerung (ASA Fruchtsäure) kombiniert mit aktivem Lifting-Komplex (Repagen). Glatter, praller, Glow.</t>
+        <v>0</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>+Temponade</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr"/>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>514594</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Aqua Dermabrasion</t>
+          <t>Wellness Körper Massagen</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>AquaDerm</t>
+          <t>Aroma Relax Rücken Massage</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>159</v>
+        <v>57</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="E64" s="5" t="inlineStr">
-        <is>
-          <t>Glow to Go. Vakuum-Tiefenreinigung, abgestimmte Wirkstoffe, für gepflegtes, aufgepolstertes Ergebnis. Gesicht + Hals + Dekolleté.</t>
+        <v>30</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>Aroma Rücken</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>Die Aroma-Öl-Massage RÜCKEN verwöhnt deine Sinne, löst Verspannungen und schenkt dir tiefes Wohlbefinden. Ein Moment nur für Dich.</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>631700</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Micro Dermabrasion</t>
+          <t>Wellness Körper Massagen</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>MicroDerm</t>
+          <t>Aroma Relax Ganzkörper</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="E65" s="5" t="inlineStr">
-        <is>
-          <t>Sanft-intensive Abtragung abgestorbener Hautzellen. Feineres, ebenmäßigeres Hautbild, Linien geglättet.</t>
+      <c r="E65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>Aroma Körper</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>Die Aroma-Öl-Massage GANZKÖRPER verwöhnt deine Sinne, löst Verspannungen und schenkt dir tiefes Wohlbefinden. Ein Moment nur für Dich.</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>631701</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Micro Dermabrasion</t>
+          <t>Wellness Körper Massagen</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>+ Hals</t>
+          <t>Lomi Loci Rücken Massage</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E66" s="5" t="inlineStr">
-        <is>
-          <t>Nur zu MicroDerm dazu buchbar.</t>
+        <v>30</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>Lomi Rücken</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>Pure Tiefenentspannung für den Rücken. Mit fließenden Bewegungen und warmem Öl löst sie Blockaden, entspannt Körper &amp; Geist. Schenkt dir neue Energie.</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>631702</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Micro Dermabrasion</t>
+          <t>Wellness Körper Massagen</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>+ Dekolleté</t>
+          <t>Lomi Lomi Ganzkörper Massage</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E67" s="5" t="inlineStr">
-        <is>
-          <t>Nur zu MicroDerm dazu buchbar.</t>
+        <v>75</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>Lomi Körper</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>Pure Tiefenentspannung für den Körper. Mit fließenden Bewegungen und warmem Öl löst sie Blockaden, entspannt Körper &amp; Geist. Schenkt dir neue Energie.</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>631703</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Micro Dermabrasion</t>
+          <t>✨VIP Treatments by Klapp SkinCare</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>MicroDerm Gesicht ON TOP</t>
+          <t>Deluxe Treatments</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>49</v>
+        <v>205</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="E68" s="5" t="inlineStr">
-        <is>
-          <t>Nur mit anderer Kosmetikbehandlung buchbar.</t>
+        <v>90</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>Deluxe Treat</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>Verwöhnen Sie sich mit einer Deluxe Erlebnis Behandlung von Klapp SkinCare. Hier legen wir den Fokus ganz klar auf die Regeneration der Haut, mit den passenden Wirkstoffen, in Kombination mit einer Auszeit für die Seele -&gt; *CellPro *Diamond *ExoGen o.ä.</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>635014</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Soft Needling</t>
+          <t>Aqua Dermabrasion</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Soft Needling</t>
+          <t>Aqua Derm NUR Serum oder Peeling</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>149</v>
+        <v>69</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="E69" s="5" t="inlineStr">
-        <is>
-          <t>Intensive Aktivierung der Haut. Hautstruktur in der Tiefe stärken, Hautbarriere aufbauen und stärken.</t>
+        <v>20</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>+Aqua Se/Pee</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>In Kombination mit einer anderen Behandlung. NUR Peeling oder NUR Serum</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>635019</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Soft Needling</t>
+          <t>Wellness Fußpflege</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>+ Exosome</t>
+          <t>+ Fußpeeling GEHWOL Fuß</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D70" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="E70" s="5" t="inlineStr">
-        <is>
-          <t>Verbessert Zell-Verbindung und -Kommunikation. Nur in Kombination buchbar.</t>
+      <c r="E70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>+Peeling Fuß</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>Als Wellness Zusatz können Sie Ihren Füßen ein intensiv abtragendes, aktivierendes und angenehmes Fußpeeling von GEHWOL zu der Wellness Fußpflege dazu buchen!</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>682891</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Soft Needling</t>
+          <t>Wellness Maniküre</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>+ Hals</t>
+          <t>+ Handmassage</t>
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="E71" s="5" t="inlineStr">
-        <is>
-          <t>Nur in Kombination mit Soft/Micro Needling buchbar.</t>
+      <c r="E71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>+Handmassage</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>Es gibt nichts schöneres als die Wellness Maniküre mit einer wohltuenden Handmassage zu beenden. Die Handmassage, kann NUR als Extra, zu jeder Behandlung dazu gebucht werden.</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>690298</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Soft Needling</t>
+          <t>➕ Zusatzbehandlungen</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>+ Dekolleté</t>
+          <t>+ Augen Deluxe Behandlung</t>
         </is>
       </c>
       <c r="C72" s="4" t="n">
@@ -2121,1095 +3373,3591 @@
       <c r="D72" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="E72" s="5" t="inlineStr">
-        <is>
-          <t>Nur in Kombination mit Soft/Micro Needling buchbar.</t>
+      <c r="E72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>+Augen Delux</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>NUR in Kombi mit einer Kosmetik Behandlung buchbar!!! Optimal für müde und geschwollene Augenpartien. Wir geben deinen Augen was sie brauchen.Eine wohltuende kühlende Massage und die richtigen Wirkstoffe. Wir regen den Lymphfluss an, minimieren die Schwellungen, durchfeuchten und glätten.</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>710737</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Micro Needling</t>
+          <t>✨TOP Kombi Behandlungen</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Micro Needling</t>
+          <t>Soft Needling meets Hyaluron</t>
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>149</v>
+        <v>239</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="E73" s="5" t="inlineStr">
-        <is>
-          <t>Regt den natürlichen Selbstheilungsprozess an. Pickelmale, Narben, Unebenheiten, Faltentiefe werden bei einer Kur effektiv vermindert.</t>
+        <v>90</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>SoftNeed.Hya</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>Intensive &amp; aktive Hyaluronsäure Kombi Behandlung. Soft Needling + 3fach Hyaluronsäure, um deine Haut zu aktivieren, zu stärken und in der Tiefe intensiv mit Feuchtigkeit zu versorgen. SOFORT 2-Fach Ergebnis-&gt; Glow + Aufgepolstert - OHNE AUSFALLZEIT !!!</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>722705</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Micro Needling</t>
+          <t>Digitale Hautanalyse mit KI</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>+ Exosome</t>
+          <t>Hautsprechstunde Hautanalyse</t>
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E74" s="5" t="inlineStr">
-        <is>
-          <t>Verbessert Zell-Verbindung und -Kommunikation. Nur in Kombination buchbar.</t>
+        <v>45</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>HautsprechSt</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
+          <t>Sie wollten schon immer mal wissen, wie es tief in Ihrer Haut aussieht? Dann ist die Hautsprechstunde genau das richtige. Wir geben Ihnen tiefe Einblicke, mit einer digitalen Hautanalyse und einer Haut- &amp; Pflege- Beratung +Behandlungsplan. Auch bei Stammkunden, in regelmäßigen abständen zu empfehlen</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>727054</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Micro Needling</t>
+          <t>Micro Dermabrasion</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>+ Hals</t>
+          <t>MicroDerm</t>
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E75" s="5" t="inlineStr">
-        <is>
-          <t>Nur in Kombination mit Soft/Micro Needling buchbar.</t>
+        <v>60</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>MicroDerm</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>Die Microdermabrasion ist eine sanfte- intensive Abtragung der abgestorbenen Hautzellen. Das Ergebnis ist ein feineres und ebenmäßigeres Hautbild, die Zellerneuerung wird angeregt und somit ist die Haut wieder aufnahmefähiger und aktiver. Linien werden geglättet und deine Haut kann wieder Leuchten.</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>772801</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Micro Needling</t>
+          <t>✨ Events ✨</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>+ Dekolleté</t>
+          <t>Hautanalyse Event am 28.2.2026</t>
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="E76" s="5" t="inlineStr">
-        <is>
-          <t>Nur in Kombination mit Soft/Micro Needling buchbar.</t>
+        <v>40</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>EVENT Hautan</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>Hautanalyse Event !!! NUR FÜR DEN 28.2. BUCHBAR!!! Du wolltest schon immer mal tief in deine Haut blicken? Dann nutz JETZT Deine Chance. GRATIS Digitale Hautanalyse mit Beratung + 10%* auf Klapp Produkte *NUR am Event Tag</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>790158</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Fruchtsäure Behandlungen</t>
+          <t>Digitale Hautanalyse mit KI</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>ASA PEEL Fruchtsäure</t>
+          <t>Gratis Hautanalyse Gutschein</t>
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="E77" s="5" t="inlineStr">
-        <is>
-          <t>Abtragende Fruchtsäure-Kombination. Linien, Fältchen, Pigmente werden minimiert. Nur buchbar Sept./Okt.–März (wg. UV-Strahlung).</t>
+        <v>30</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>HautScanGrat</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>GRATIS Digitale Hautanalyse, NUR mit einem Gutschein buchbar !!!</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>792765</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Fruchtsäure Behandlungen</t>
+          <t>Soft Needling</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>ASA Fruchtsäure KUR</t>
+          <t>Soft Needling</t>
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>447</v>
+        <v>149</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="E78" s="5" t="inlineStr">
-        <is>
-          <t>3er-Kur (empfohlen für optimales Ergebnis). Inkl. gratis Heimpflege im Wert von 30 €.</t>
+        <v>60</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>Soft Needli</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>Soft Needling ist eine intensive Aktivierung der Haut. Die Hautstrucktur wird in der Tiefe, mit hochkonzentrierten Wirkstoffen angeregt, gestärkt und regeneriert. Optimal um deine Hautbarriere aufzubauen und zu stärken. OHNE AUSFALLZEIT!</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>800571</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Klassische Gesichts Behandlungen</t>
+          <t>Micro Needling</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Relax Behandlung</t>
+          <t>+ Exosome</t>
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>129</v>
+        <v>15</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="E79" s="5" t="inlineStr">
-        <is>
-          <t>Entspannende Verwöhnbehandlung für eine kleine Auszeit vom Alltag, individuell auf die Haut abgestimmt.</t>
+        <v>5</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>+ Exosome</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>NEU!!! Optimal um die Zell-Verbindung und Zell-Kommunikation zu verbessern. Besonders gut geeignet bei den ersten Anzeichen der Hautalterung und bei Problem Haut jeglicher Art. NUR in Verbindung mit einem Micro / Soft Needling buchbar !!!</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>801792</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Klassische Gesichts Behandlungen</t>
+          <t>✨TOP Kombi Behandlungen</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Clean &amp; Activ Behandlung</t>
+          <t>MicroDerm meets AquaDerm</t>
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>93</v>
+        <v>199</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="E80" s="5" t="inlineStr">
-        <is>
-          <t>Intensive Ausreinigungsbehandlung für ein sauberes, geklärtes Hautbild.</t>
+        <v>80</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>Micro+Aqua</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>Ein intensives Behandlungserlebnis mit sofortigem Glow und einer strahlenden Haut .Abgestorbene Hautzellen werden effektiv abgetragen, dein Hautbild wird verfeinert, Linien minimiert und Wirkstoffe werden tief eingeschleust. Einmaliges Sofort Ergebnis. Samtweiches &amp; strahlendes Hautbild</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>807617</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Zusatzbehandlungen</t>
+          <t>Soft Needling</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>+ Augen Deluxe Behandlung</t>
+          <t>+ Exosome</t>
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="E81" s="5" t="inlineStr">
-        <is>
-          <t>Für müde, geschwollene Augenpartien. Nur in Kombi buchbar.</t>
+        <v>5</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>+Exosome</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>NEU!!! Optimal um die Zell-Verbindung und Zell-Kommunikation zu verbessern. Besonders gut geeignet bei den ersten Anzeichen der Hautalterung und bei Problem Haut jeglicher Art. NUR in Verbindung mit einem Micro / Soft Needling buchbar !!!</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>807729</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Zusatzbehandlungen</t>
+          <t>Soft Needling</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>+ Ampulle</t>
+          <t>+ Hals</t>
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D82" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="E82" s="5" t="inlineStr">
-        <is>
-          <t>Nur in Kombination mit einer Kosmetikbehandlung buchbar.</t>
+      <c r="E82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>+Hals</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>+Hals. NUR in Kombination mit der Soft/ Micro Needling Behandlung buchbar !!!</t>
+        </is>
+      </c>
+      <c r="I82" s="3" t="inlineStr">
+        <is>
+          <t>807730</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Zusatzbehandlungen</t>
+          <t>Soft Needling</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>+ Spezial Maske</t>
+          <t>+ Dekolleté</t>
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E83" s="5" t="inlineStr">
-        <is>
-          <t>Nur als Extra zu einer Kosmetikbehandlung buchbar.</t>
+        <v>10</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>+Dekolleté</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>+Dekollete. NUR in Kombination mit der Soft/ Micro Needling Behandlung buchbar !!!</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>807731</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Zusatzbehandlungen</t>
+          <t>✨ Events ✨</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>+ Wimpern färben</t>
+          <t>Event Vorbereiten</t>
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="E84" s="5" t="inlineStr">
-        <is>
-          <t>Nur in Verbindung mit einer anderen Behandlung buchbar.</t>
+        <v>5</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>Event Orga!</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="inlineStr"/>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>807735</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Zusatzbehandlungen</t>
+          <t>💥NEU FORMA - Hautstraffung (Radiofrequenz) InMode</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>+ Augenbrauen färben</t>
+          <t>FORMA Augen</t>
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>14</v>
+        <v>129</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E85" s="5" t="inlineStr">
-        <is>
-          <t>Nur in Verbindung mit einer anderen Behandlung buchbar.</t>
+        <v>40</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>Forma Eye</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>FORMA strafft gezielt ihren kompletten Augenbereich. Elastizitätsverlust am oberen Augenlid wird minimiert und unterm Auge wird es sichtbar straffer. Radiofrequenz aktiviert Collagen in der tiefe und baut neue Collagen Strukturen auf.Für eine langfristig straffere Augenpartie !6er KUR erforderlich!</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>807738</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Zusatzbehandlungen</t>
+          <t>💥NEU DIOLAZE - Dauerhafte Haarentfernung InMode</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>+ Augenbrauen zupfen</t>
+          <t>Achseln</t>
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E86" s="5" t="inlineStr">
-        <is>
-          <t>Nur in Verbindung mit einer anderen Behandlung buchbar.</t>
+        <v>30</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>Achseln</t>
+        </is>
+      </c>
+      <c r="H86" s="5" t="inlineStr">
+        <is>
+          <t>Bitte Beachten!!! MINDESTENS! 24 Std. vorher rasieren. 4 Wo. vorher nicht zupfen, Epilieren oder Waxen. 2 Wo. vorher kein Aluminiumhaltiges Deo, kein intensives Peeling, kein Selbstbräuner, kein Solarium, intensive Bräunung. 4-6 Wo.vorher KEINE Medikamente, Antibiotika oä. (bitte vorher info an uns)</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>807739</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Zusatzbehandlungen</t>
+          <t>Digitale Hautanalyse mit KI</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>+ Augenbrauen Wachsen</t>
+          <t>+ Digitale Hautananlyse</t>
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E87" s="5" t="inlineStr">
-        <is>
-          <t>Nur in Verbindung mit einer anderen Behandlung buchbar.</t>
+        <v>20</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>+ HautScan</t>
+        </is>
+      </c>
+      <c r="H87" s="5" t="inlineStr">
+        <is>
+          <t>Sie sind sich unsicher, was mit ihrer Haut los ist oder möchten mal tief in ihre Haut blicken, um ihren Hautzustand und ihre Heimpflege zu optimieren? Dann buchen sie sich eine Digitale Hautananlyse. NUR in Kombination mit einer Kosmetik Behandlung buchbar.</t>
+        </is>
+      </c>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>809281</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Zusatzbehandlungen</t>
+          <t>Digitale Hautanalyse mit KI</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>+ Kinn/Oberlippe zupfen</t>
+          <t>+ Hautanalyse Stammkunden</t>
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E88" s="5" t="inlineStr">
-        <is>
-          <t>Nur in Verbindung mit einer anderen Behandlung buchbar.</t>
+        <v>10</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>+Scan Gratis</t>
+        </is>
+      </c>
+      <c r="H88" s="5" t="inlineStr">
+        <is>
+          <t>NUR für unsere Stammkunden, NUR für uns buchbar. Hautbild Kontrolle. GRATIS</t>
+        </is>
+      </c>
+      <c r="I88" s="3" t="inlineStr">
+        <is>
+          <t>809282</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Zusatzbehandlungen</t>
+          <t>✨ Aktuelle Angebote</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>+ Kinn/Oberlippe zupfen Intensiv</t>
+          <t>Vitamin C Fresh Up Power</t>
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>24</v>
+        <v>159</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="E89" s="5" t="inlineStr">
-        <is>
-          <t>Bei vielen Haaren. Nur in Verbindung mit einer anderen Behandlung buchbar.</t>
+        <v>70</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>Vit.C.Fresh</t>
+        </is>
+      </c>
+      <c r="H89" s="5" t="inlineStr">
+        <is>
+          <t>Erlebe die Kombination aus Mikrodermabrasion und Vitamin C. Wir befreien deine Haut sanft, aber effektiv von Hautschüppchen und sorgen damit, in Verbindung mit hochdosiertem Vitamin C, für ein frisches und ebenmäßiges Hautbild. Optimal nach dem Winter,für einen tollen Glow.</t>
+        </is>
+      </c>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t>809283</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Zusatzbehandlungen</t>
+          <t>✨ Aktuelle Angebote</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>+ Collagen Vlies OnTop Gesicht</t>
+          <t>Wellness Fußpflege SPA</t>
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E90" s="5" t="inlineStr">
-        <is>
-          <t>Spezielles Collagen-Vlies. Nur als Extra buchbar.</t>
+        <v>50</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>Fuß Spa</t>
+        </is>
+      </c>
+      <c r="H90" s="5" t="inlineStr">
+        <is>
+          <t>Aktion vom 19.3.- 30.5. -&gt; Verwöhn Behandlung für deine Winterfüße. Ein Fußpeeling trägt sanft deine Hautschüppchen ab, danach folgt die Wellness Fußpflege. Zum Abschluss verwöhnen wir dich mit einer entspannenden Fußmassage.</t>
+        </is>
+      </c>
+      <c r="I90" s="3" t="inlineStr">
+        <is>
+          <t>809284</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Zusatzbehandlungen</t>
+          <t>✨ Aktuelle Angebote</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>+ Collagen Vlies Dekolleté</t>
+          <t>Soft Needling Exosome</t>
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>22</v>
+        <v>139</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E91" s="5" t="inlineStr">
-        <is>
-          <t>Spezielles Collagen-Vlies. Nur als Extra buchbar.</t>
+        <v>60</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>SoftNe.Exo</t>
+        </is>
+      </c>
+      <c r="H91" s="5" t="inlineStr">
+        <is>
+          <t>Ist ihre Haut im Ungleichgewicht, wirkt müde und gestresst?Dann empfehlen wir das Soft Needling.Wir starten mit einer entspannenden Kopfmassage.Im Anschluss aktivieren wir die Zellregeneration,stärken die Hautbarriere &amp;fördern die Mikrozirkulation.Für eine gestärkte Haut</t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>815502</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Zusatzbehandlungen</t>
+          <t>➕ Zusatzbehandlungen</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Oberlippe wachsen</t>
+          <t>+ Collagen Vlies OnTop Gesicht</t>
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="E92" s="5" t="inlineStr">
-        <is>
-          <t>Warmwachs Oberlippe.</t>
+        <v>5</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>+Collag.Vlie</t>
+        </is>
+      </c>
+      <c r="H92" s="5" t="inlineStr">
+        <is>
+          <t>Spezielles Collagen Vlies für besondere Hautbedürfnisse. NUR als EXTRA zu einer Kosmetik Behandlung buchbar.</t>
+        </is>
+      </c>
+      <c r="I92" s="3" t="inlineStr">
+        <is>
+          <t>815503</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Zusatzbehandlungen</t>
+          <t>✨ Aktuelle Angebote</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Oberlippe + Kinn wachsen</t>
+          <t>OnTop Hals Dekoltee (Soft Needling/Needling/Micro)</t>
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="E93" s="5" t="inlineStr">
-        <is>
-          <t>Warmwachs Oberlippe + Kinn.</t>
+        <v>10</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>+Hals+Dekolt</t>
+        </is>
+      </c>
+      <c r="H93" s="5" t="inlineStr">
+        <is>
+          <t>Hals Dekolleté ON TOP. Vergiss deinen Hals und Dekollete nicht und buch dir eine intensive Hals/Dekollete Regeneration. Zu  jeder Soft Needling/ Needling/ Micro Behandlung dazu buchbar. Und auch zu den Aktions Behandlungen dazu buchbar.</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>815504</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Wellness Fußpflege</t>
+          <t>➕ Zusatzbehandlungen</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Wellness Fußpflege</t>
+          <t>+ Collagen Vlies Dekoltee</t>
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="E94" s="5" t="inlineStr">
-        <is>
-          <t>Pflegendes Fußbad, Nägel schneiden/formen, Hornhaut, Massage, individuelle Abschlusspflege.</t>
+        <v>5</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>+Coll.VliesD</t>
+        </is>
+      </c>
+      <c r="H94" s="5" t="inlineStr">
+        <is>
+          <t>Spezielles Collagen Vlies für besondere Hautbedürfnisse. NUR als EXTRA zu einer Kosmetik Behandlung buchbar.</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>815507</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Wellness Fußpflege</t>
+          <t>💥NEU FORMA - Hautstraffung (Radiofrequenz) InMode</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>+ Nagellack Fuß</t>
+          <t>FORMA 3 Zonen</t>
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>16</v>
+        <v>319</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="E95" s="5" t="inlineStr">
-        <is>
-          <t>Alessandro Nagellack, 4 Schichten, ca. 4 Wochen haltbar.</t>
+        <v>105</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>Forma 3Zonen</t>
+        </is>
+      </c>
+      <c r="H95" s="5" t="inlineStr">
+        <is>
+          <t>FORMA strafft gezielt Ihre Gesichts Konturen, Elastizitätsverlust wird stark minimiert und Sie gewinnen eine langfristig straffere und festere Haut zurück. Radiofrequenz aktiviert Collagen in der Tiefe und baut, über Wärme, neue Collagen Strukturen auf !6er KUR erforderlich!</t>
+        </is>
+      </c>
+      <c r="I95" s="3" t="inlineStr">
+        <is>
+          <t>816616</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Wellness Fußpflege</t>
+          <t>💥NEU FORMA - Hautstraffung (Radiofrequenz) InMode</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>+ UV-Nagellack Fuß</t>
+          <t>FORMA 4 Zonen</t>
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>31</v>
+        <v>399</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="E96" s="5" t="inlineStr">
-        <is>
-          <t>Alessandro UV-Nagellack, 4 Schichten.</t>
+        <v>110</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>Forma 4Zonen</t>
+        </is>
+      </c>
+      <c r="H96" s="5" t="inlineStr">
+        <is>
+          <t>*zb. Jawline +Wangen (oben+unten) +Stirn. FORMA strafft gezielt Ihre Gesichts Konturen, Elastizitätsverlust wird stark minimiert und Sie gewinnen eine langfristig straffere und festere Haut zurück. Radiofrequenz aktiviert Collagen in der Tiefe und baut, über Wärme, neue Collagen Strukturen auf.</t>
+        </is>
+      </c>
+      <c r="I96" s="3" t="inlineStr">
+        <is>
+          <t>816618</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Wellness Fußpflege</t>
+          <t>💥NEU FORMA - Hautstraffung (Radiofrequenz) InMode</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>+ Fußpeeling GEHWOL Fuß</t>
+          <t>FORMA Hals</t>
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>10</v>
+        <v>129</v>
       </c>
       <c r="D97" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E97" s="5" t="inlineStr">
-        <is>
-          <t>Intensiv abtragendes Fußpeeling.</t>
+        <v>40</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>Forma Hals</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>FORMA strafft gezielt Ihre Gesichts Konturen, Elastizitätsverlust wird stark minimiert und Sie gewinnen eine langfristig straffere und festere Haut zurück. Radiofrequenz aktiviert Collagen in der Tiefe und baut, über Wärme, neue Collagen Strukturen auf !6er KUR erforderlich!</t>
+        </is>
+      </c>
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t>816623</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Wellness Fußpflege</t>
+          <t>💥NEU FORMA - Hautstraffung (Radiofrequenz) InMode</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>+ Fußmassage</t>
+          <t>FORMA Beratungsgespräch + Digitaler Hautanalyse KI</t>
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="D98" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E98" s="5" t="inlineStr">
-        <is>
-          <t>Wohltuende Fußmassage.</t>
+        <v>30</v>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>FORMA Berat+</t>
+        </is>
+      </c>
+      <c r="H98" s="5" t="inlineStr">
+        <is>
+          <t>Umfangreiches Beratungsgespräch inklusive einer ausführlichen Aufklärung über die FORMA Radiofrequenz. Zusätzlich machen wir eine Digitalen Hautanalyse mit KI, um uns Ihre Haut und das Collagen auch in der Tiefe genauer anzugucken. Bei einer anschließenden Forma- Kur, wird der Betrag verrechnet.</t>
+        </is>
+      </c>
+      <c r="I98" s="3" t="inlineStr">
+        <is>
+          <t>816661</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Wellness Fußpflege</t>
+          <t>💥NEU FORMA - Hautstraffung (Radiofrequenz) InMode</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>+ SPA Fuß</t>
+          <t>FORMA GRATIS Beratungsgespräch</t>
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="E99" s="5" t="inlineStr">
-        <is>
-          <t>Peeling + Packung + Massage für die Füße.</t>
+      <c r="E99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>FORMA Info</t>
+        </is>
+      </c>
+      <c r="H99" s="5" t="inlineStr">
+        <is>
+          <t>Gratis Beratungsgespräch inklusive einer ausführlichen Aufklärung über die FORMA Radiofrequenz. Wir gucken uns gemeinsam Ihre Gesichtspartien an und ich berate Sie ehrlich, ob wir die Festigkeit mit dem FORMA wieder zurück gewinnen können.</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>816666</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Wellness Maniküre</t>
+          <t>💥NEU FORMA - Hautstraffung (Radiofrequenz) InMode</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Wellness Maniküre</t>
+          <t>FORMA OnTop Augen</t>
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="E100" s="5" t="inlineStr">
-        <is>
-          <t>Intensive Hand- und Nagelpflege mit Alessandro-Produkten, inkl. Handbad und Nagelpflege.</t>
+        <v>35</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>OnTop Eye</t>
+        </is>
+      </c>
+      <c r="H100" s="5" t="inlineStr">
+        <is>
+          <t>Die FORMA Radiofrequenz Augenbehandlung OnTop, kann NUR zu einer Kosmetik Behandlung dazu gebucht werden! NICHT kombinierbar mit einer Fruchtsäure Behandlung.</t>
+        </is>
+      </c>
+      <c r="I100" s="3" t="inlineStr">
+        <is>
+          <t>816676</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Wellness Maniküre</t>
+          <t>💥NEU FORMA - Hautstraffung (Radiofrequenz) InMode</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>+ Nagellack Maniküre</t>
+          <t>FORMA OnTop Hals</t>
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="E101" s="5" t="inlineStr">
-        <is>
-          <t>Alessandro Nagellack, 4 Schichten.</t>
+        <v>35</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>OnTop Hals</t>
+        </is>
+      </c>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>Die FORMA Radiofrequenz Halsbehandlung OnTop, kann NUR zu einer Kosmetik Behandlung dazu gebucht werden! NICHT kombinierbar mit einer Fruchtsäure Behandlung.</t>
+        </is>
+      </c>
+      <c r="I101" s="3" t="inlineStr">
+        <is>
+          <t>816679</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Wellness Maniküre</t>
+          <t>💥NEU FORMA - Hautstraffung (Radiofrequenz) InMode</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>+ Handmassage</t>
+          <t>FORMA Lippen</t>
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>12</v>
+        <v>129</v>
       </c>
       <c r="D102" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E102" s="5" t="inlineStr">
-        <is>
-          <t>Wohltuende Handmassage.</t>
+        <v>40</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>Forma Lippen</t>
+        </is>
+      </c>
+      <c r="H102" s="5" t="inlineStr">
+        <is>
+          <t>FORMA strafft gezielt deine Lippenfältchen, Elastizitätsverlust wird stark minimiert und Sie gewinnen eine langfristig straffere und festere umliegende Lippenpartie zurück. Radiofrequenz aktiviert Collagen in der Tiefe und baut, über Wärme, neue Collagen Strukturen auf !6er KUR erforderlich!</t>
+        </is>
+      </c>
+      <c r="I102" s="3" t="inlineStr">
+        <is>
+          <t>816694</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Wellness Maniküre</t>
+          <t>💥NEU FORMA - Hautstraffung (Radiofrequenz) InMode</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>+ SPA Hand</t>
+          <t>FORMA OnTop Lippen</t>
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="E103" s="5" t="inlineStr">
-        <is>
-          <t>Peeling + Packung + Massage für die Hände.</t>
+        <v>35</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>OnTop Lippen</t>
+        </is>
+      </c>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>Die FORMA Radiofrequenz Lippenbehandlung OnTop, kann NUR zu einer Kosmetik Behandlung dazu gebucht werden! NICHT kombinierbar mit einer Fruchtsäure Behandlung.</t>
+        </is>
+      </c>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>816695</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Gel Verstärkung Fingernägel</t>
+          <t>✨ Aktuelle Angebote</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>Natur Nagel Verstärkung NEU</t>
+          <t>AquaDerm meets Soft Needling Exosome</t>
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>94</v>
+        <v>225</v>
       </c>
       <c r="D104" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="E104" s="5" t="inlineStr">
-        <is>
-          <t>Verstärkung der Naturnägel mit Gel, ohne Verlängerung.</t>
+        <v>90</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t>Aqua/Soft Ex</t>
+        </is>
+      </c>
+      <c r="H104" s="5" t="inlineStr">
+        <is>
+          <t>Intensive Kombination für intensive Hautbedürfnisse. Mehr Glow. Mehr Balance. Mehr Regeneration für Ihre Haut. Intensive Tiefenreinigung, einschleusen von Hyaluronsäure, anregen der Zellaktivität durch Exosome, stärken der Hautbarriere, porenverfeinernd, aufpolsternd.</t>
+        </is>
+      </c>
+      <c r="I104" s="3" t="inlineStr">
+        <is>
+          <t>818103</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Gel Verstärkung Fingernägel</t>
+          <t>💥NEU FORMA - Hautstraffung (Radiofrequenz) InMode</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>Neue Gel Modellage mit Verlängerung Tips/Schablone</t>
+          <t>FORMA OnTop 3 Zonen*</t>
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="D105" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="E105" s="5" t="inlineStr">
-        <is>
-          <t>Neue Gel-Modellage mit Verlängerung (Tips oder Schablonentechnik).</t>
+        <v>90</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>OnTop 3Zo.</t>
+        </is>
+      </c>
+      <c r="H105" s="5" t="inlineStr">
+        <is>
+          <t>*zb. Jawline (Doppelkinn)+ untere +obere Wangen. Die FORMA Radiofrequenz Behandlung OnTop, kann NUR zu einer Kosmetik Behandlung dazu gebucht werden! NICHT kombinierbar mit einer Fruchtsäure Behandlung.</t>
+        </is>
+      </c>
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t>819422</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Gel Verstärkung Fingernägel</t>
+          <t>💥NEU FORMA - Hautstraffung (Radiofrequenz) InMode</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Auffüllen Gel Nägel</t>
+          <t>FOMRA OnTop 4 Zonen*</t>
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="E106" s="5" t="inlineStr">
-        <is>
-          <t>Auffüllen der Gel-Nägel nach ca. 3–4 Wochen.</t>
+        <v>90</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t>OnTop 4Zon.</t>
+        </is>
+      </c>
+      <c r="H106" s="5" t="inlineStr">
+        <is>
+          <t>*zb. Jawline +Wangen (oben+unten) +Stirn. FORMA Radiofrequenz 4 Zonen OnTop, kann NUR zu einer Kosmetik Behandlung dazu gebucht werden! NICHT kombinierbar mit einer Fruchtsäure Behandlung.</t>
+        </is>
+      </c>
+      <c r="I106" s="3" t="inlineStr">
+        <is>
+          <t>819423</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Gel Verstärkung Fingernägel</t>
+          <t>💥NEU FORMA - Hautstraffung (Radiofrequenz) InMode</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>+ Farbgel/French/Babyboomer</t>
+          <t>FORMA 6er KUR</t>
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="E107" s="5" t="inlineStr">
-        <is>
-          <t>Als Extra zu einer Gel-Nagel-Behandlung.</t>
+        <v>5</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>FORMA 6erKUR</t>
+        </is>
+      </c>
+      <c r="H107" s="5" t="inlineStr">
+        <is>
+          <t>10% Rabatt auf die Auswählte FORMA KUR. Bitte zu der FORMA Beh. dazu buchen!</t>
+        </is>
+      </c>
+      <c r="I107" s="3" t="inlineStr">
+        <is>
+          <t>819424</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Gel Verstärkung Fingernägel</t>
+          <t>💥NEU FORMA - Hautstraffung (Radiofrequenz) InMode</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>Gel entfernen inkl. Pflege</t>
+          <t>ANGEBOT 5+1 Kur</t>
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D108" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="E108" s="5" t="inlineStr">
-        <is>
-          <t>Gel-Modellage entfernen inklusive Pflege.</t>
+        <v>5</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t>AKTION 5+1</t>
+        </is>
+      </c>
+      <c r="H108" s="5" t="inlineStr">
+        <is>
+          <t>FORMA Kennenlern Aktion 5x FORMA Behandlungen bezahlen + 1 GRATIS. Bitte zu einer KUR dazu buchen NUR für kurze Zeit!!!</t>
+        </is>
+      </c>
+      <c r="I108" s="3" t="inlineStr">
+        <is>
+          <t>819425</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Wimpernlifting - Browlift</t>
+          <t>💥NEU FORMA - Hautstraffung (Radiofrequenz) InMode</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>Wimpernlifting inkl. Keratin Versiegelung</t>
+          <t>ANGEBOT 7+2 Kur</t>
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D109" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="E109" s="5" t="inlineStr">
-        <is>
-          <t>Natürlicher, perfekter Augenaufschlag für die Naturwimpern.</t>
+        <v>5</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>AKTION 7+2</t>
+        </is>
+      </c>
+      <c r="H109" s="5" t="inlineStr">
+        <is>
+          <t>Forma Kennenlern Aktion 7x FORMA Behandlungen bezahlen + 2 GRATIS. Bitte zu einer Kur dazu buchen. NUR für eine kurze Zeit !!!</t>
+        </is>
+      </c>
+      <c r="I109" s="3" t="inlineStr">
+        <is>
+          <t>819426</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Wimpernlifting - Browlift</t>
+          <t>💥NEU FORMA - Hautstraffung (Radiofrequenz) InMode</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Wimpernwelle inkl. Keratin Versiegelung</t>
+          <t>FORMA 8er KUR</t>
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="E110" s="5" t="inlineStr">
-        <is>
-          <t>Bringt Schwung in gerade Naturwimpern.</t>
+        <v>5</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>FORMA 8erKUR</t>
+        </is>
+      </c>
+      <c r="H110" s="5" t="inlineStr">
+        <is>
+          <t>10% Rabatt auf die ausgewählte FORMA KUR. Bitte zu der FORMA Beh. dazu buchen!</t>
+        </is>
+      </c>
+      <c r="I110" s="3" t="inlineStr">
+        <is>
+          <t>819461</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Wimpernlifting - Browlift</t>
+          <t>💥NEU FORMA - Hautstraffung (Radiofrequenz) InMode</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Browlift inkl. Keratin Versiegelung</t>
+          <t>FORMA Jawline inkl. unteren Wangenbereich</t>
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>59</v>
+        <v>129</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="E111" s="5" t="inlineStr">
-        <is>
-          <t>Lässt Augenbrauen voller und dichter erscheinen.</t>
+        <v>45</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>Forma Jawlin</t>
+        </is>
+      </c>
+      <c r="H111" s="5" t="inlineStr">
+        <is>
+          <t>*Doppelkinn inkl. unteren Wangenbereich. FORMA strafft gezielt Ihre Gesichts Konturen, Elastizitätsverlust wird stark minimiert und Sie gewinnen eine langfristig straffere und festere Haut zurück. Radiofrequenz aktiviert Collagen in der Tiefe und baut, über Wärme, neue Collagen Strukturen auf.</t>
+        </is>
+      </c>
+      <c r="I111" s="3" t="inlineStr">
+        <is>
+          <t>819745</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Wimpernlifting - Browlift</t>
+          <t>💥NEU FORMA - Hautstraffung (Radiofrequenz) InMode</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>+ Wimpern färben Lifting/Welle</t>
+          <t>FORMA OnTop Jawline inkl. unterem Wangenbereich</t>
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="E112" s="5" t="inlineStr">
-        <is>
-          <t>Als Extra zum Wimpernlifting/-welle.</t>
+        <v>40</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="inlineStr">
+        <is>
+          <t>OnTop Jaw/Wa</t>
+        </is>
+      </c>
+      <c r="H112" s="5" t="inlineStr">
+        <is>
+          <t>*Jawline inkl. unterem Wangenbereich. Die FORMA Radiofrequenz Behandlung OnTop, kann NUR zu einer Kosmetik Behandlung dazu gebucht werden! NICHT kombinierbar mit einer Fruchtsäure Behandlung.</t>
+        </is>
+      </c>
+      <c r="I112" s="3" t="inlineStr">
+        <is>
+          <t>819747</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Wimpernlifting - Browlift</t>
+          <t>💥NEU DIOLAZE - Dauerhafte Haarentfernung InMode</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>+ Augenbrauen färben Browlift</t>
+          <t>GRATIS Beratungsgespräch Inkl. Haar- &amp; Hautanalyse</t>
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D113" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E113" s="5" t="inlineStr">
-        <is>
-          <t>Als Extra zum Browlift.</t>
+        <v>30</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>Gratis Haarf</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="inlineStr">
+        <is>
+          <t>Sie möchten sich über die Dauerhafte Haarentfernung informieren oder sind sich noch unsicher? Dann buchen Sie sich dieses GRATIS Beratungsgespräch und wir räumen alle Ihre Fragen aus dem Weg. Inklusive einer Haar- &amp; Hautanalyse und dem ein oder anderen Test- Schuß..</t>
+        </is>
+      </c>
+      <c r="I113" s="3" t="inlineStr">
+        <is>
+          <t>819748</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Wimpern &amp; Augenbrauen - Einzelbehandlung</t>
+          <t>💥NEU DIOLAZE - Dauerhafte Haarentfernung InMode</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Wimpern färben</t>
+          <t>FIRST DATE! Laser</t>
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D114" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="E114" s="5" t="inlineStr">
-        <is>
-          <t>Außerhalb einer Behandlung.</t>
+      <c r="E114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>First Date</t>
+        </is>
+      </c>
+      <c r="H114" s="5" t="inlineStr">
+        <is>
+          <t>Bitte zu Ihrer ERSTEN Laser Behandlung dazu buchen, damit wir genügend Zeit für die erste Behandlung haben.</t>
+        </is>
+      </c>
+      <c r="I114" s="3" t="inlineStr">
+        <is>
+          <t>819749</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Wimpern &amp; Augenbrauen - Einzelbehandlung</t>
+          <t>💥NEU DIOLAZE - Dauerhafte Haarentfernung InMode</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Augenbrauen färben</t>
+          <t>Oberlippe</t>
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="E115" s="5" t="inlineStr">
-        <is>
-          <t>Außerhalb einer Behandlung.</t>
+        <v>20</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>Oberlippe</t>
+        </is>
+      </c>
+      <c r="H115" s="5" t="inlineStr">
+        <is>
+          <t>Bitte Beachten!!! MINDESTENS! 24 Std. vorher rasieren. 4 Wo. vorher nicht zupfen, Epilieren oder Waxen. 2 Wo.vorher kein intensives Peeling, kein Selbstbräuner, kein Solarium, keine intensive Bräunung. 4-6 Wo.vorher KEINE Medikamente, Antibiotika oä. (bitte vorher info an uns)</t>
+        </is>
+      </c>
+      <c r="I115" s="3" t="inlineStr">
+        <is>
+          <t>819750</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Wimpern &amp; Augenbrauen - Einzelbehandlung</t>
+          <t>💥NEU DIOLAZE - Dauerhafte Haarentfernung InMode</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>Augenbrauen zupfen</t>
+          <t>Kinn</t>
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="E116" s="5" t="inlineStr">
-        <is>
-          <t>Außerhalb einer Behandlung.</t>
+        <v>20</v>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>Kinn</t>
+        </is>
+      </c>
+      <c r="H116" s="5" t="inlineStr">
+        <is>
+          <t>Bitte Beachten!!! MINDESTENS! 24 Std. vorher rasieren. 4 Wo. vorher nicht zupfen, Epilieren oder Waxen. 2 Wo.vorher kein intensives Peeling, kein Selbstbräuner, kein Solarium, keine intensive Bräunung. 4-6 Wo.vorher KEINE Medikamente, Antibiotika oä. (bitte vorher info an uns)</t>
+        </is>
+      </c>
+      <c r="I116" s="3" t="inlineStr">
+        <is>
+          <t>819751</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Wimpern &amp; Augenbrauen - Einzelbehandlung</t>
+          <t>💥NEU DIOLAZE  🔥Must Have Pakete🔥</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>Augenbrauen Wachsen</t>
+          <t>Kinn + Hals</t>
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="D117" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="E117" s="5" t="inlineStr">
-        <is>
-          <t>Außerhalb einer Behandlung.</t>
+        <v>30</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>Kinn+Hals</t>
+        </is>
+      </c>
+      <c r="H117" s="5" t="inlineStr">
+        <is>
+          <t>Bitte Beachten!!! MINDESTENS! 24 Std. vorher rasieren. 4 Wo. vorher nicht zupfen, Epilieren oder Waxen. 2 Wo.vorher kein intensives Peeling, kein Selbstbräuner, kein Solarium, keine intensive Bräunung. 4-6 Wo.vorher KEINE Medikamente, Antibiotika oä. (bitte vorher info an uns)</t>
+        </is>
+      </c>
+      <c r="I117" s="3" t="inlineStr">
+        <is>
+          <t>819752</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Wellness Körper Massagen</t>
+          <t>💥NEU DIOLAZE - Dauerhafte Haarentfernung InMode</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>Aroma Relax Rücken Massage</t>
+          <t>Bikini Zone</t>
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="E118" s="5" t="inlineStr">
-        <is>
-          <t>Aroma-Öl-Massage Rücken, löst Verspannungen.</t>
+        <v>20</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="inlineStr">
+        <is>
+          <t>Bikini</t>
+        </is>
+      </c>
+      <c r="H118" s="5" t="inlineStr">
+        <is>
+          <t>Bitte Beachten!!! MINDESTENS! 24 Std. vorher rasieren. 4 Wo. vorher nicht zupfen, Epilieren oder Waxen. 2 Wo.vorher kein intensives Peeling, kein Selbstbräuner, kein Solarium, keine intensive Bräunung. 4-6 Wo.vorher KEINE Medikamente, Antibiotika oä. (bitte vorher info an uns)</t>
+        </is>
+      </c>
+      <c r="I118" s="3" t="inlineStr">
+        <is>
+          <t>819753</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Wellness Körper Massagen</t>
+          <t>💥NEU DIOLAZE - Dauerhafte Haarentfernung InMode</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>Aroma Relax Ganzkörper</t>
+          <t>Intim Bereich</t>
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="D119" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>Intim</t>
+        </is>
+      </c>
+      <c r="H119" s="5" t="inlineStr">
+        <is>
+          <t>Bitte Beachten!!! MINDESTENS! 24 Std. vorher rasieren. 4 Wo. vorher nicht zupfen, Epilieren oder Waxen. 2 Wo.vorher kein intensives Peeling, kein Selbstbräuner, kein Solarium, keine intensive Bräunung. 4-6 Wo.vorher KEINE Medikamente, Antibiotika oä. (bitte vorher info an uns)</t>
+        </is>
+      </c>
+      <c r="I119" s="3" t="inlineStr">
+        <is>
+          <t>819754</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>💥NEU DIOLAZE  🔥Must Have Pakete🔥</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>MUST HAVE Achseln + Bikini</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="n">
+        <v>155</v>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>Achs+Biki</t>
+        </is>
+      </c>
+      <c r="H120" s="5" t="inlineStr">
+        <is>
+          <t>Bitte Beachten!!! MINDESTENS! 24 Std. vorher rasieren. 4 Wo. vorher nicht zupfen, Epilieren oder Waxen. 2 Wo. vorher kein Aluminiumhaltiges Deo, kein intensives Peeling, kein Selbstbräuner, kein Solarium, intensive Bräunung. 4-6 Wo.vorher KEINE Medikamente, Antibiotika oä. (bitte vorher info an uns)</t>
+        </is>
+      </c>
+      <c r="I120" s="3" t="inlineStr">
+        <is>
+          <t>819756</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>💥NEU DIOLAZE - Dauerhafte Haarentfernung InMode</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>Bein Unterschenkel</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="n">
+        <v>149</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>BeinUnter</t>
+        </is>
+      </c>
+      <c r="H121" s="5" t="inlineStr">
+        <is>
+          <t>Bitte Beachten!!! MINDESTENS! 24 Std. vorher rasieren. 4 Wo. vorher nicht zupfen, Epilieren oder Waxen. 2 Wo.vorher kein intensives Peeling, kein Selbstbräuner, kein Solarium, keine intensive Bräunung. 4-6 Wo.vorher KEINE Medikamente, Antibiotika oä. (bitte vorher info an uns)</t>
+        </is>
+      </c>
+      <c r="I121" s="3" t="inlineStr">
+        <is>
+          <t>819759</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>💥NEU DIOLAZE - Dauerhafte Haarentfernung InMode</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>Bein Oberschenkel</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="n">
+        <v>159</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>BeinOber</t>
+        </is>
+      </c>
+      <c r="H122" s="5" t="inlineStr">
+        <is>
+          <t>Bitte Beachten!!! MINDESTENS! 24 Std. vorher rasieren. 4 Wo. vorher nicht zupfen, Epilieren oder Waxen. 2 Wo.vorher kein intensives Peeling, kein Selbstbräuner, kein Solarium, keine intensive Bräunung. 4-6 Wo.vorher KEINE Medikamente, Antibiotika oä. (bitte vorher info an uns)</t>
+        </is>
+      </c>
+      <c r="I122" s="3" t="inlineStr">
+        <is>
+          <t>819760</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>💥NEU DIOLAZE  🔥Must Have Pakete🔥</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>Beine Komplett</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="n">
+        <v>275</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t>BeineKompl</t>
+        </is>
+      </c>
+      <c r="H123" s="5" t="inlineStr">
+        <is>
+          <t>Bitte Beachten!!! MINDESTENS! 24 Std. vorher rasieren. 4 Wo. vorher nicht zupfen, Epilieren oder Waxen. 2 Wo.vorher kein intensives Peeling, kein Selbstbräuner, kein Solarium, keine intensive Bräunung. 4-6 Wo.vorher KEINE Medikamente, Antibiotika oä. (bitte vorher info an uns)</t>
+        </is>
+      </c>
+      <c r="I123" s="3" t="inlineStr">
+        <is>
+          <t>819761</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>💥NEU DIOLAZE  🔥Must Have Pakete🔥</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>Oberlippe + Kinn</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="n">
+        <v>79</v>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="inlineStr">
+        <is>
+          <t>Oberl+Kinn</t>
+        </is>
+      </c>
+      <c r="H124" s="5" t="inlineStr">
+        <is>
+          <t>Bitte Beachten!!! MINDESTENS! 24 Std. vorher rasieren. 4 Wo. vorher nicht zupfen, Epilieren oder Waxen. 2 Wo.vorher kein intensives Peeling, kein Selbstbräuner, kein Solarium, keine intensive Bräunung. 4-6 Wo.vorher KEINE Medikamente, Antibiotika oä. (bitte vorher info an uns)</t>
+        </is>
+      </c>
+      <c r="I124" s="3" t="inlineStr">
+        <is>
+          <t>819763</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>💥NEU DIOLAZE  🔥Must Have Pakete🔥</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>MUST HAVE Achseln + Intim Bereich</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="n">
+        <v>199</v>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>Ach/Intim</t>
+        </is>
+      </c>
+      <c r="H125" s="5" t="inlineStr">
+        <is>
+          <t>Bitte Beachten!!! MINDESTENS! 24 Std. vorher rasieren. 4 Wo. vorher nicht zupfen, Epilieren oder Waxen. 2Wochen vorher kein Aluminiumhaltiges Deo, intensives Peeling, kein Selbstbräuner, kein Solarium, intensive Bräunung. 4-6 Wo.vorher KEINE Medikamente, Antibiotika oä. (bitte vorher info an uns)</t>
+        </is>
+      </c>
+      <c r="I125" s="3" t="inlineStr">
+        <is>
+          <t>819765</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>💥NEU DIOLAZE  🔥Must Have Pakete🔥</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>Arme Komplett</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="n">
+        <v>199</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="inlineStr">
+        <is>
+          <t>ArmeKompl</t>
+        </is>
+      </c>
+      <c r="H126" s="5" t="inlineStr">
+        <is>
+          <t>Bitte Beachten!!! MINDESTENS! 24 Std. vorher rasieren. 4 Wo. vorher nicht zupfen, Epilieren oder Waxen. 2 Wo.vorher kein intensives Peeling, kein Selbstbräuner, kein Solarium, keine intensive Bräunung. 4-6 Wo.vorher KEINE Medikamente, Antibiotika oä. (bitte vorher info an uns)</t>
+        </is>
+      </c>
+      <c r="I126" s="3" t="inlineStr">
+        <is>
+          <t>819766</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>💥NEU DIOLAZE - Dauerhafte Haarentfernung InMode</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>Unterarme</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="n">
+        <v>109</v>
+      </c>
+      <c r="D127" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G127" s="3" t="inlineStr">
+        <is>
+          <t>Unterarm</t>
+        </is>
+      </c>
+      <c r="H127" s="5" t="inlineStr">
+        <is>
+          <t>Bitte Beachten!!! MINDESTENS! 24 Std. vorher rasieren. 4 Wo. vorher nicht zupfen, Epilieren oder Waxen. 2 Wo.vorher kein intensives Peeling, kein Selbstbräuner, kein Solarium, keine intensive Bräunung. 4-6 Wo.vorher KEINE Medikamente, Antibiotika oä. (bitte vorher info an uns)</t>
+        </is>
+      </c>
+      <c r="I127" s="3" t="inlineStr">
+        <is>
+          <t>819767</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>💥NEU DIOLAZE - Dauerhafte Haarentfernung InMode</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>Oberarm</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="n">
+        <v>119</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G128" s="3" t="inlineStr">
+        <is>
+          <t>Oberarm</t>
+        </is>
+      </c>
+      <c r="H128" s="5" t="inlineStr">
+        <is>
+          <t>Bitte Beachten!!! MINDESTENS! 24 Std. vorher rasieren. 4 Wo. vorher nicht zupfen, Epilieren oder Waxen. 2 Wo.vorher kein intensives Peeling, kein Selbstbräuner, kein Solarium, keine intensive Bräunung. 4-6 Wo.vorher KEINE Medikamente, Antibiotika oä. (bitte vorher info an uns)</t>
+        </is>
+      </c>
+      <c r="I128" s="3" t="inlineStr">
+        <is>
+          <t>819768</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>💥NEU DIOLAZE - Dauerhafte Haarentfernung InMode</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>Rücken</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="n">
+        <v>149</v>
+      </c>
+      <c r="D129" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G129" s="3" t="inlineStr">
+        <is>
+          <t>Rücken</t>
+        </is>
+      </c>
+      <c r="H129" s="5" t="inlineStr">
+        <is>
+          <t>Bitte Beachten!!! MINDESTENS! 24 Std. vorher rasieren. 4 Wo. vorher nicht zupfen, Epilieren oder Waxen. 2 Wo.vorher kein intensives Peeling, kein Selbstbräuner, kein Solarium, keine intensive Bräunung. 4-6 Wo.vorher KEINE Medikamente, Antibiotika oä. (bitte vorher info an uns)</t>
+        </is>
+      </c>
+      <c r="I129" s="3" t="inlineStr">
+        <is>
+          <t>819769</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>💥NEU DIOLAZE - Dauerhafte Haarentfernung InMode</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>Brust</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="n">
+        <v>109</v>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="inlineStr">
+        <is>
+          <t>Brust</t>
+        </is>
+      </c>
+      <c r="H130" s="5" t="inlineStr">
+        <is>
+          <t>Bitte Beachten!!! MINDESTENS! 24 Std. vorher rasieren. 4 Wo. vorher nicht zupfen, Epilieren oder Waxen. 2 Wo.vorher kein intensives Peeling, kein Selbstbräuner, kein Solarium, keine intensive Bräunung. 4-6 Wo.vorher KEINE Medikamente, Antibiotika oä. (bitte vorher info an uns)</t>
+        </is>
+      </c>
+      <c r="I130" s="3" t="inlineStr">
+        <is>
+          <t>819770</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>💥NEU DIOLAZE - Dauerhafte Haarentfernung InMode</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>Bauch</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="n">
+        <v>99</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>Bauch</t>
+        </is>
+      </c>
+      <c r="H131" s="5" t="inlineStr">
+        <is>
+          <t>Bitte Beachten!!! MINDESTENS! 24 Std. vorher rasieren. 4 Wo. vorher nicht zupfen, Epilieren oder Waxen. 2 Wo.vorher kein intensives Peeling, kein Selbstbräuner, kein Solarium, keine intensive Bräunung. 4-6 Wo.vorher KEINE Medikamente, Antibiotika oä. (bitte vorher info an uns)</t>
+        </is>
+      </c>
+      <c r="I131" s="3" t="inlineStr">
+        <is>
+          <t>819771</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>💥NEU DIOLAZE  🔥Must Have Pakete🔥</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>Herren Brust + Bauch</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="n">
+        <v>199</v>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="inlineStr">
+        <is>
+          <t>Hr.Br+Bauch</t>
+        </is>
+      </c>
+      <c r="H132" s="5" t="inlineStr">
+        <is>
+          <t>Bitte Beachten!!! MINDESTENS! 24 Std. vorher rasieren. 4 Wo. vorher nicht zupfen, Epilieren oder Waxen. 2 Wo.vorher kein intensives Peeling, kein Selbstbräuner, kein Solarium, keine intensive Bräunung. 4-6 Wo.vorher KEINE Medikamente, Antibiotika oä. (bitte vorher info an uns)</t>
+        </is>
+      </c>
+      <c r="I132" s="3" t="inlineStr">
+        <is>
+          <t>819772</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>➕ Zusatzbehandlungen</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>+ Kinn / Oberlippe zupfen Intensiv</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="inlineStr">
+        <is>
+          <t>+zpf.Intens.</t>
+        </is>
+      </c>
+      <c r="H133" s="5" t="inlineStr">
+        <is>
+          <t>Oberlippe und/oder Kinn zupfen Intensiv, bei vielen Haaren. NUR in Verbindung mit einer anderen Behandlung buchbar !!!</t>
+        </is>
+      </c>
+      <c r="I133" s="3" t="inlineStr">
+        <is>
+          <t>820937</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Micro Dermabrasion</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>+ Hals</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="inlineStr">
+        <is>
+          <t>+Mic.Hals</t>
+        </is>
+      </c>
+      <c r="H134" s="5" t="inlineStr">
+        <is>
+          <t>+Hals. NUR zu einer MICRODERM dazu buchbar!!!</t>
+        </is>
+      </c>
+      <c r="I134" s="3" t="inlineStr">
+        <is>
+          <t>820962</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>✨ Events ✨</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>FORMA Kennenlern Behandlung</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="inlineStr">
+        <is>
+          <t>Event FORMA</t>
+        </is>
+      </c>
+      <c r="H135" s="5" t="inlineStr">
+        <is>
+          <t>FORMA Kennenlern kurz Behandlung NUR am 6.Juni am Glow Skin &amp; Hairfree Event buchbar!!! Spür die Kraft der Radiofrequenz. Wir aktivieren auf natürlichem Weg, dein Collagen in der Tiefe, für eine straffere Haut und klarere Konturen.</t>
+        </is>
+      </c>
+      <c r="I135" s="3" t="inlineStr">
+        <is>
+          <t>822331</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>💥NEU DIOLAZE - Dauerhafte Haarentfernung InMode</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>Herren Brust</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="n">
+        <v>115</v>
+      </c>
+      <c r="D136" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E136" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="inlineStr">
+        <is>
+          <t>Hr.Brust</t>
+        </is>
+      </c>
+      <c r="H136" s="5" t="inlineStr">
+        <is>
+          <t>Bitte Beachten!!! MINDESTENS! 24 Std. vorher rasieren. 4 Wo. vorher nicht zupfen, Epilieren oder Waxen. 2 Wo.vorher kein intensives Peeling, kein Selbstbräuner, kein Solarium, keine intensive Bräunung. 4-6 Wo.vorher KEINE Medikamente, Antibiotika oä. (bitte vorher info an uns)</t>
+        </is>
+      </c>
+      <c r="I136" s="3" t="inlineStr">
+        <is>
+          <t>823726</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>💥NEU DIOLAZE - Dauerhafte Haarentfernung InMode</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>Herren Bauch</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="n">
+        <v>129</v>
+      </c>
+      <c r="D137" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E137" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G137" s="3" t="inlineStr">
+        <is>
+          <t>Hr. Bauch</t>
+        </is>
+      </c>
+      <c r="H137" s="5" t="inlineStr">
+        <is>
+          <t>Bitte Beachten!!! MINDESTENS! 24 Std. vorher rasieren. 4 Wo. vorher nicht zupfen, Epilieren oder Waxen. 2 Wo.vorher kein intensives Peeling, kein Selbstbräuner, kein Solarium, keine intensive Bräunung. 4-6 Wo.vorher KEINE Medikamente, Antibiotika oä. (bitte vorher info an uns)</t>
+        </is>
+      </c>
+      <c r="I137" s="3" t="inlineStr">
+        <is>
+          <t>823727</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>💥NEU DIOLAZE - Dauerhafte Haarentfernung InMode</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>Herren Nacken</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="n">
+        <v>69</v>
+      </c>
+      <c r="D138" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E138" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G138" s="3" t="inlineStr">
+        <is>
+          <t>Hr. Nacken</t>
+        </is>
+      </c>
+      <c r="H138" s="5" t="inlineStr">
+        <is>
+          <t>Bitte Beachten!!! MINDESTENS! 24 Std. vorher rasieren. 4 Wo. vorher nicht zupfen, Epilieren oder Waxen. 2 Wo.vorher kein intensives Peeling, kein Selbstbräuner, kein Solarium, keine intensive Bräunung. 4-6 Wo.vorher KEINE Medikamente, Antibiotika oä. (bitte vorher info an uns)</t>
+        </is>
+      </c>
+      <c r="I138" s="3" t="inlineStr">
+        <is>
+          <t>823728</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>💥NEU DIOLAZE - Dauerhafte Haarentfernung InMode</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>Herren Schultern</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="n">
+        <v>89</v>
+      </c>
+      <c r="D139" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E139" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t>Hr. Schulter</t>
+        </is>
+      </c>
+      <c r="H139" s="5" t="inlineStr">
+        <is>
+          <t>Bitte Beachten!!! MINDESTENS! 24 Std. vorher rasieren. 4 Wo. vorher nicht zupfen, Epilieren oder Waxen. 2 Wo.vorher kein intensives Peeling, kein Selbstbräuner, kein Solarium, keine intensive Bräunung. 4-6 Wo.vorher KEINE Medikamente, Antibiotika oä. (bitte vorher info an uns)</t>
+        </is>
+      </c>
+      <c r="I139" s="3" t="inlineStr">
+        <is>
+          <t>823729</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>💥NEU DIOLAZE - Dauerhafte Haarentfernung InMode</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>Herren Rücken</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="n">
+        <v>169</v>
+      </c>
+      <c r="D140" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="E140" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="inlineStr">
+        <is>
+          <t>Hr. Rücken</t>
+        </is>
+      </c>
+      <c r="H140" s="5" t="inlineStr">
+        <is>
+          <t>Bitte Beachten!!! MINDESTENS! 24 Std. vorher rasieren. 4 Wo. vorher nicht zupfen, Epilieren oder Waxen. 2 Wo.vorher kein intensives Peeling, kein Selbstbräuner, kein Solarium, keine intensive Bräunung. 4-6 Wo.vorher KEINE Medikamente, Antibiotika oä. (bitte vorher info an uns)</t>
+        </is>
+      </c>
+      <c r="I140" s="3" t="inlineStr">
+        <is>
+          <t>823730</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>💥NEU DIOLAZE - Dauerhafte Haarentfernung InMode</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>Herren Teil- Rücken</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="n">
+        <v>79</v>
+      </c>
+      <c r="D141" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E141" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G141" s="3" t="inlineStr">
+        <is>
+          <t>Hr.Teil-Rück</t>
+        </is>
+      </c>
+      <c r="H141" s="5" t="inlineStr">
+        <is>
+          <t>Bitte Beachten!!! MINDESTENS! 24 Std. vorher rasieren. 4 Wo. vorher nicht zupfen, Epilieren oder Waxen. 2 Wo.vorher kein intensives Peeling, kein Selbstbräuner, kein Solarium, keine intensive Bräunung. 4-6 Wo.vorher KEINE Medikamente, Antibiotika oä. (bitte vorher info an uns)</t>
+        </is>
+      </c>
+      <c r="I141" s="3" t="inlineStr">
+        <is>
+          <t>823731</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>💥NEU DIOLAZE - Dauerhafte Haarentfernung InMode</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>Herren Achseln</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="D142" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E142" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G142" s="3" t="inlineStr">
+        <is>
+          <t>Hr. Achseln</t>
+        </is>
+      </c>
+      <c r="H142" s="5" t="inlineStr">
+        <is>
+          <t>Bitte Beachten!!! MINDESTENS! 24 Std. vorher rasieren. 4 Wo. vorher nicht zupfen, Epilieren oder Waxen. 2Wo. vorher kein Aluminiumhaltiges Deo, kein intensives Peeling, kein Selbstbräuner, kein Solarium, intensive Bräunung. 4-6 Wo.vorher KEINE Medikamente, Antibiotika oä. (bitte vorher info an uns)</t>
+        </is>
+      </c>
+      <c r="I142" s="3" t="inlineStr">
+        <is>
+          <t>823732</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>💥NEU DIOLAZE  🔥Must Have Pakete🔥</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>Herren Rücken + Schulter + Nacken</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="n">
+        <v>259</v>
+      </c>
+      <c r="D143" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="E119" s="5" t="inlineStr">
-        <is>
-          <t>Aroma-Öl-Massage Ganzkörper, löst Verspannungen.</t>
+      <c r="E143" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G143" s="3" t="inlineStr">
+        <is>
+          <t>Hr.Rü+Sch+Na</t>
+        </is>
+      </c>
+      <c r="H143" s="5" t="inlineStr">
+        <is>
+          <t>Bitte Beachten!!! MINDESTENS! 24 Std. vorher rasieren. 4 Wo. vorher nicht zupfen, Epilieren oder Waxen. 2 Wo.vorher kein intensives Peeling, kein Selbstbräuner, kein Solarium, keine intensive Bräunung. 4-6 Wo.vorher KEINE Medikamente, Antibiotika oä. (bitte vorher info an uns)</t>
+        </is>
+      </c>
+      <c r="I143" s="3" t="inlineStr">
+        <is>
+          <t>823734</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>💥NEU DIOLAZE  🔥Must Have Pakete🔥</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>Herren Brust + Bauch + Rücken</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="n">
+        <v>329</v>
+      </c>
+      <c r="D144" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="E144" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G144" s="3" t="inlineStr">
+        <is>
+          <t>Hr.Br+Bau+Rü</t>
+        </is>
+      </c>
+      <c r="H144" s="5" t="inlineStr">
+        <is>
+          <t>Bitte Beachten!!! MINDESTENS! 24 Std. vorher rasieren. 4 Wo. vorher nicht zupfen, Epilieren oder Waxen. 2 Wo.vorher kein intensives Peeling, kein Selbstbräuner, kein Solarium, keine intensive Bräunung. 4-6 Wo.vorher KEINE Medikamente, Antibiotika oä. (bitte vorher info an uns)</t>
+        </is>
+      </c>
+      <c r="I144" s="3" t="inlineStr">
+        <is>
+          <t>823735</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>💥NEU DIOLAZE  🔥Must Have Pakete🔥</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>Herren Arme Komplett</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="n">
+        <v>219</v>
+      </c>
+      <c r="D145" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="E145" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G145" s="3" t="inlineStr">
+        <is>
+          <t>Hr.ArmeKompl</t>
+        </is>
+      </c>
+      <c r="H145" s="5" t="inlineStr">
+        <is>
+          <t>Bitte Beachten!!! MINDESTENS! 24 Std. vorher rasieren. 4 Wo. vorher nicht zupfen, Epilieren oder Waxen. 2 Wo.vorher kein intensives Peeling, kein Selbstbräuner, kein Solarium, keine intensive Bräunung. 4-6 Wo.vorher KEINE Medikamente, Antibiotika oä. (bitte vorher info an uns)</t>
+        </is>
+      </c>
+      <c r="I145" s="3" t="inlineStr">
+        <is>
+          <t>823737</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>💥NEU DIOLAZE  🔥Must Have Pakete🔥</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>Herren Beine Komplett</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="n">
+        <v>295</v>
+      </c>
+      <c r="D146" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E146" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F146" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G146" s="3" t="inlineStr">
+        <is>
+          <t>Hr.BeineKomp</t>
+        </is>
+      </c>
+      <c r="H146" s="5" t="inlineStr">
+        <is>
+          <t>Bitte Beachten!!! MINDESTENS! 24 Std. vorher rasieren. 4 Wo. vorher nicht zupfen, Epilieren oder Waxen. 2 Wo.vorher kein intensives Peeling, kein Selbstbräuner, kein Solarium, keine intensive Bräunung. 4-6 Wo.vorher KEINE Medikamente, Antibiotika oä. (bitte vorher info an uns)</t>
+        </is>
+      </c>
+      <c r="I146" s="3" t="inlineStr">
+        <is>
+          <t>823738</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>💥NEU DIOLAZE  🔥Must Have Pakete🔥</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>Herren Rücken + Schulter</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="n">
+        <v>229</v>
+      </c>
+      <c r="D147" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E147" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G147" s="3" t="inlineStr">
+        <is>
+          <t>Hr.Rück+Schu</t>
+        </is>
+      </c>
+      <c r="H147" s="5" t="inlineStr">
+        <is>
+          <t>Bitte Beachten!!! MINDESTENS! 24 Std. vorher rasieren. 4 Wo. vorher nicht zupfen, Epilieren oder Waxen. 2 Wo.vorher kein intensives Peeling, kein Selbstbräuner, kein Solarium, keine intensive Bräunung. 4-6 Wo.vorher KEINE Medikamente, Antibiotika oä. (bitte vorher info an uns)</t>
+        </is>
+      </c>
+      <c r="I147" s="3" t="inlineStr">
+        <is>
+          <t>823754</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>💥NEU DIOLAZE  🔥Must Have Pakete🔥</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>Herren Nacken + Schulter</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="n">
+        <v>135</v>
+      </c>
+      <c r="D148" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E148" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F148" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G148" s="3" t="inlineStr">
+        <is>
+          <t>Hr.Na+Schul</t>
+        </is>
+      </c>
+      <c r="H148" s="5" t="inlineStr">
+        <is>
+          <t>Bitte Beachten!!! MINDESTENS! 24 Std. vorher rasieren. 4 Wo. vorher nicht zupfen, Epilieren oder Waxen. 2 Wo.vorher kein intensives Peeling, kein Selbstbräuner, kein Solarium, keine intensive Bräunung. 4-6 Wo.vorher KEINE Medikamente, Antibiotika oä. (bitte vorher info an uns)</t>
+        </is>
+      </c>
+      <c r="I148" s="3" t="inlineStr">
+        <is>
+          <t>823770</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>💥NEU DIOLAZE  🔥Must Have Pakete🔥</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>MUST HAVE Achseln + Intim + Unterschenkel</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="n">
+        <v>315</v>
+      </c>
+      <c r="D149" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="E149" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F149" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G149" s="3" t="inlineStr">
+        <is>
+          <t>Ach+In+Un</t>
+        </is>
+      </c>
+      <c r="H149" s="5" t="inlineStr">
+        <is>
+          <t>Bitte Beachten!!! MINDESTENS! 24 Std. vorher rasieren. 4 Wo. vorher nicht zupfen, Epilieren oder Waxen. 2 Wo. vorher kein Aluminiumhaltiges Deo, kein intensives Peeling, kein Selbstbräuner, kein Solarium, intensive Bräunung. 4-6 Wo.vorher KEINE Medikamente, Antibiotika oä. (bitte vorher info an uns)</t>
+        </is>
+      </c>
+      <c r="I149" s="3" t="inlineStr">
+        <is>
+          <t>823773</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>💥NEU DIOLAZE  🔥Must Have Pakete🔥</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>MUST HAVE Achseln + Intim Bereich + Beine Komplett</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="n">
+        <v>439</v>
+      </c>
+      <c r="D150" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="E150" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G150" s="3" t="inlineStr">
+        <is>
+          <t>Ach+In+BeKom</t>
+        </is>
+      </c>
+      <c r="H150" s="5" t="inlineStr">
+        <is>
+          <t>Bitte Beachten!!! MINDESTENS! 24 Std. vorher rasieren. 4 Wo. vorher nicht zupfen, Epilieren oder Waxen. 2 Wo. vorher kein Aluminiumhaltiges Deo, kein intensives Peeling, kein Selbstbräuner, kein Solarium, intensive Bräunung. 4-6 Wo.vorher KEINE Medikamente, Antibiotika oä. (bitte vorher info an uns)</t>
+        </is>
+      </c>
+      <c r="I150" s="3" t="inlineStr">
+        <is>
+          <t>823960</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>💥NEU FORMA - Hautstraffung (Radiofrequenz) InMode</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>FORMA 1 Zone</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="n">
+        <v>119</v>
+      </c>
+      <c r="D151" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="E151" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G151" s="3" t="inlineStr">
+        <is>
+          <t>Forma 1Zonen</t>
+        </is>
+      </c>
+      <c r="H151" s="5" t="inlineStr">
+        <is>
+          <t>FORMA strafft gezielt Ihre Gesichts Konturen, Elastizitätsverlust wird stark minimiert und Sie gewinnen eine langfristig straffere und festere Haut zurück. Radiofrequenz aktiviert Collagen in der Tiefe und baut, über Wärme, neue Collagen Strukturen auf !6er KUR erforderlich!</t>
+        </is>
+      </c>
+      <c r="I151" s="3" t="inlineStr">
+        <is>
+          <t>825726</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>✨ Events ✨</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>GRATIS DIOLAZE Hairfree Termin</t>
+        </is>
+      </c>
+      <c r="C152" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D152" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E152" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="inlineStr">
+        <is>
+          <t>Event Diolaz</t>
+        </is>
+      </c>
+      <c r="H152" s="5" t="inlineStr">
+        <is>
+          <t>GRATIS Hairfree Termin mit dem DIOLAZE NUR am 6.Juni Glow Skin &amp; Hairfree Event buchbar!!! Sicher Dir Deinen gratis Termin, um zu spüren, wie effektiv diese Behandlung ist. GRATIS: Visitenkarten Größe</t>
+        </is>
+      </c>
+      <c r="I152" s="3" t="inlineStr">
+        <is>
+          <t>826124</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>✨ Events ✨</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>GLOW SKIN &amp; HAIRFREE EVENT 6.6.</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D153" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E153" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G153" s="3" t="inlineStr">
+        <is>
+          <t>InMode Event</t>
+        </is>
+      </c>
+      <c r="H153" s="5" t="inlineStr"/>
+      <c r="I153" s="3" t="inlineStr">
+        <is>
+          <t>826126</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>💥NEU FORMA - Hautstraffung (Radiofrequenz) InMode</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>FORMA 2 Zonen</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="n">
+        <v>219</v>
+      </c>
+      <c r="D154" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="E154" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G154" s="3" t="inlineStr">
+        <is>
+          <t>Forma 2Zonen</t>
+        </is>
+      </c>
+      <c r="H154" s="5" t="inlineStr">
+        <is>
+          <t>FORMA strafft gezielt Ihre Gesichts Konturen, Elastizitätsverlust wird stark minimiert und Sie gewinnen eine langfristig straffere und festere Haut zurück. Radiofrequenz aktiviert Collagen in der Tiefe und baut, über Wärme, neue Collagen Strukturen auf !6er KUR erforderlich!</t>
+        </is>
+      </c>
+      <c r="I154" s="3" t="inlineStr">
+        <is>
+          <t>826808</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>✨ Events ✨</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>SkinCare &amp; Hairfree Event am 5.9.</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D155" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E155" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G155" s="3" t="inlineStr">
+        <is>
+          <t>Skin&amp;Hairfre</t>
+        </is>
+      </c>
+      <c r="H155" s="5" t="inlineStr">
+        <is>
+          <t>GEPLANTES SkinCare &amp; Haifree Event am Sa.5.9.2026 von 9:00-14:00Uhr. GRATIS Hairfree Termine und FORMA kennenlern Behandlungen. Sichern Sie sich frühzeitig Ihren Termin oder kommen spontan vorbei!!! Wir freuen uns über jeden einzelnen.</t>
+        </is>
+      </c>
+      <c r="I155" s="3" t="inlineStr">
+        <is>
+          <t>840582</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Micro Dermabrasion</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>+ Dekolleté</t>
+        </is>
+      </c>
+      <c r="C156" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D156" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E156" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G156" s="3" t="inlineStr">
+        <is>
+          <t>+Mic.Dekoll</t>
+        </is>
+      </c>
+      <c r="H156" s="5" t="inlineStr">
+        <is>
+          <t>+ Dekolleté. NUR zu einer MICRODERM dazu buchbar!!!</t>
+        </is>
+      </c>
+      <c r="I156" s="3" t="inlineStr">
+        <is>
+          <t>840583</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>Micro Dermabrasion</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>MicroDerm Gesicht ON TOP</t>
+        </is>
+      </c>
+      <c r="C157" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="D157" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E157" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F157" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G157" s="3" t="inlineStr">
+        <is>
+          <t>+MicroOnTop</t>
+        </is>
+      </c>
+      <c r="H157" s="5" t="inlineStr">
+        <is>
+          <t>MicroDerm ON TOP. NUR mit einer anderen Kosmetik Behandlung buchbar. Um ein intensiveres Hautergebnis zu erreichen. Raue und abgestorbene Hautschüppchen werden intensiv abgetragen und die Zellerneuerung wird angeregt. Für ein weiches, ebenmäßiges und feineres Hautbild.</t>
+        </is>
+      </c>
+      <c r="I157" s="3" t="inlineStr">
+        <is>
+          <t>840584</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Micro Dermabrasion</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>+ Massage</t>
+        </is>
+      </c>
+      <c r="C158" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="D158" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E158" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F158" s="3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G158" s="3" t="inlineStr">
+        <is>
+          <t>+Mic.Massage</t>
+        </is>
+      </c>
+      <c r="H158" s="5" t="inlineStr">
+        <is>
+          <t>+ Massage. NUR MICRODERM dazu buchbar !</t>
+        </is>
+      </c>
+      <c r="I158" s="3" t="inlineStr">
+        <is>
+          <t>840585</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Soft Needling</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>+ Massage</t>
+        </is>
+      </c>
+      <c r="C159" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="D159" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E159" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" s="3" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G159" s="3" t="inlineStr">
+        <is>
+          <t>+SoftN+Massa</t>
+        </is>
+      </c>
+      <c r="H159" s="5" t="inlineStr">
+        <is>
+          <t>+ Massage. NUR in Kombination mit einer SOFT NEEDLING Behandlung buchbar</t>
+        </is>
+      </c>
+      <c r="I159" s="3" t="inlineStr">
+        <is>
+          <t>840586</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E119"/>
+  <autoFilter ref="A1:I159"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3232,32 +6980,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>need</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>behandlung</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>dauer</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>preis</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>produkt</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Begründung</t>
         </is>
@@ -3552,14 +7300,440 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Hinweis:</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>need-Spalte muss exakt einem der 9 festen Beauty-Needs-Werte entsprechen (siehe App-Logik). Quelle aller Preise/Behandlungen: studiobookr.com/beauty-lounge-66137, abgerufen 2026-08-23.</t>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>need-Spalte muss exakt einem der 9 festen Beauty-Needs-Werte entsprechen (siehe App-Logik). Preise/Behandlungen direkt aus dem Studiolution-Export (siehe unten), Stand 2026-08-23.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Kategorie</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Bezeichnung</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Meeting/ Einarbeiten/ Schulung</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Schulung</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Meeting/ Einarbeiten/ Schulung</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Einarbeiten</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Meeting/ Einarbeiten/ Schulung</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Büro</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Büro</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Dekorieren</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Fensterdeko</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Dekorieren</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dekorieren</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Meeting/ Einarbeiten/ Schulung</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Personal Gespräch</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Reserviert/ Extra Zeit</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Reserviert, Warte auf Rückruf!!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Ausfall Gebühr!!!</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ausfall Gebühr</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Meeting/ Einarbeiten/ Schulung</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Aussendienst</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Reserviert/ Extra Zeit</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Warteliste!</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Meeting/ Einarbeiten/ Schulung</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Probearbeiten</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Meeting/ Einarbeiten/ Schulung</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Bewerbungsgespräch</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Wichtig!!!</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Blumen Lieferung</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Reserviert/ Extra Zeit</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Extra Zeit Kosmetik Neukundin 15min.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Reserviert/ Extra Zeit</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Extra Zeit Kosmetik Beratung 15min.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Wichtig!!!</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kälte Klima Düser Wartung</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Reserviert/ Extra Zeit</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Vorbereitung Feierabend</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Reserviert/ Extra Zeit</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Extra Zeit 10min</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Reserviert/ Extra Zeit</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Extra Zeit 15min.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Reserviert/ Extra Zeit</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Extra Zeit 20min</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Meeting/ Einarbeiten/ Schulung</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Aktions Behandlung vorbereiten</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Meeting/ Einarbeiten/ Schulung</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Praktikantin</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Meeting/ Einarbeiten/ Schulung</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Former Einarbeiten/ Schulung</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Meeting/ Einarbeiten/ Schulung</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Diolaze XL Einarbeiten/ Schulung</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Meeting/ Einarbeiten/ Schulung</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>NISV Online</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Meeting/ Einarbeiten/ Schulung</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>NISV PRAXIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Meeting/ Einarbeiten/ Schulung</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Video bearbeiten -Aktions Behandlung-</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Wichtig!!!</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Papiermüll raus stellen</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Meeting/ Einarbeiten/ Schulung</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Video drehen</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Meeting/ Einarbeiten/ Schulung</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Fotos machen mit Fotograf</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Meeting/ Einarbeiten/ Schulung</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Behandlung Schulung</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Hinweis:</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Diese Positionen sind interne Kalenderblöcke (Schulung, Büro, Reserviert, Ausfallgebühr etc.) aus dem Studiolution-Export, keine buchbaren Kundenleistungen — deshalb nicht in 'Alle Leistungen' enthalten.</t>
         </is>
       </c>
     </row>
